--- a/internal_doc/05.测试设计/可靠性测试/主子表故障测试_review.xlsx
+++ b/internal_doc/05.测试设计/可靠性测试/主子表故障测试_review.xlsx
@@ -12,7 +12,7 @@
     <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$G$145</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$G$142</definedName>
   </definedNames>
   <calcPr calcId="124519"/>
 </workbook>
@@ -973,7 +973,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A147" authorId="0">
+    <comment ref="A143" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1038,7 +1038,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C151" authorId="0">
+    <comment ref="C147" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1069,10 +1069,204 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="351" uniqueCount="162">
-  <si>
-    <t>1、普通拥塞
-2、时间设置超过9s延迟</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="347" uniqueCount="143">
+  <si>
+    <t>dataRG连续降备</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>dataRG备节点故障</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>dataRG主节点所在服务器CPU耗尽</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>dataRG备节点所在服务器CPU耗尽</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>catalog主节点正常重启</t>
+  </si>
+  <si>
+    <t>catalog备节点正常重启</t>
+  </si>
+  <si>
+    <t>dataRG主节点正常重启</t>
+  </si>
+  <si>
+    <t>catalog备节点异常重启</t>
+  </si>
+  <si>
+    <t>dataRG主节点异常重启</t>
+  </si>
+  <si>
+    <t>catalog主节点异常重启</t>
+  </si>
+  <si>
+    <t>网络单通（低优先级）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>断网后组内重新选主；恢复网络后查看是否从新的主节点同步数据，数据完整且跟新主数据一致；挂载成功在对应主表做基本操作成功(如insert数据)；</t>
+  </si>
+  <si>
+    <t>断网后组内连续降备选主；恢复网络后查看是否从新的主节点同步数据；挂载成功在对应主表做基本操作成功(如insert数据)；主表catalog数据完整且一致；</t>
+  </si>
+  <si>
+    <t>重启后组内重新选主；恢复后查看是否从新的主节点同步数据，数据完整且跟新主数据一致；挂载成功在对应主表做基本操作成功(如insert数据)；</t>
+  </si>
+  <si>
+    <t>断网后组内重新选主；恢复网络后查看是否从新的主节点同步数据，数据完整且跟新主数据一致；分离成功在该普通主表做基本操作成功(如insert数据)；</t>
+  </si>
+  <si>
+    <t>断网后组内重新选主；恢复网络后查看是否从新的主节点同步数据，数据完整且跟新主数据一致；aggregate成功，返回结果正确；aggregate失败正常报错，网络恢复后可以继续查询；</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>dataRG备节点网络闪断</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>catalog备节点网络闪断</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>dataRG主节点网络闪断</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>catalog主节点网络拥塞</t>
+  </si>
+  <si>
+    <t>dataRG备节点网络拥塞</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>catalog备节点网络拥塞</t>
+  </si>
+  <si>
+    <t>dataRG主节点网络拥塞</t>
+  </si>
+  <si>
+    <t>insert/upsert/remove</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>重复detachCL多次，catalog主节点的时间跳变</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>正常操作过程中时间改变</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>dataRG备节点时间跳变</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>时间跳变后dataRG数据不丢失，各节点数据完整一致；基本操作成功，数据查询结果正确；</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>attachCL成功，各节点数据完整一致；</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>操作成功，各节点数据完整一致；</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>插入16M大小的数据</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>对不同主表并发attach多个子表</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>dataRG备节点所在服务器磁盘满</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>dataRG备节点正常重启</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>组合异常(包括同一异常多次出现)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>dataRG主节点XX异常</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>主节点所在主机异常重启</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>备节点所在主机异常重启</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>同节点正常重启</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>等友滨确认后再考虑具体测试点</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>dataRG备节点XX异常</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>断网后组内重新选主；恢复网络后查看是否从新的主节点同步数据，数据完整且跟新主数据一致；子表挂载成功在对应主表做基本操作成功(如insert数据)；</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>dataRG主节点与dataRG备节点网络单通</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>coord主节点与dataRG主、备节点网络单通</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>闪断不超过选主的最小时间7s则不触发选主，attachCL成功，在主表做基本操作成功；闪断超过7s后组内重新选主，恢复网络后查看是否从新的主节点同步数据，数据完整且跟新主数据一致；挂载成功在对应主表做基本操作成功(如insert数据)；</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>网络拥塞达到选主条件时重新选主；恢复网络后查看是否从新的主节点同步数据，数据完整且跟新主数据一致；挂载成功在对应主表做基本操作成功(如insert数据)；</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>测试场景</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>测试子特性</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>测试项</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>测试子项</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>测试点</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>测试描述</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>备注</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -1080,15 +1274,23 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>网络闪断</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>网络拥塞</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>主机异常重启</t>
+    <t>主子表</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>attachCL</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>catalog主节点断网</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>catalog备节点断网</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>恢复网络后检测数据完整且跟新主数据一致；</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -1096,266 +1298,8 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>断网后组内重新选主；恢复网络后查看是否从新的主节点同步数据，数据完整且跟新主数据一致；insert成功，数据完整，可正常查询；insert失败数据丢失，不存在垃圾数据；</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>测试场景</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>测试子特性</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>测试子项</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>测试点</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>测试描述</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>备注</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>主子表</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>catalog主节点断网</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>catalog备节点断网</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>恢复网络后检测数据完整且跟新主数据一致；</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>dataRG主节点断网</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>dataRG连续降备</t>
     <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>dataRG备节点故障</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>catalog主节点断网</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>主表range，子表range，多分区键，在主表insert</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>CPU耗尽</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>故障恢复后数据没有丢失，重新操作成功</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>内存耗尽</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>时间跳变</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>大压力高并发</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>取典型值，执行过程中随机取值</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>磁盘满</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>节点正常重启</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>节点异常重启</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>主机正常重启</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ulimit配置异常(堆栈、句柄、线程数、虚存)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>恢复故障后，主备节点数据一致</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>次数取值？随机值</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>不影响操作，故障恢复后数据一致</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>主表range，子表hash，AutoSplit：true,多个分区键，在主表insert</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>主表range，子表hash，AutoSplit：false,在主表remove</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>断网后组内连续降备选主；恢复网络后查看是否从新的主节点同步数据；upsert成功，数据被更新；upsert失败数据不被更新，数据正常存在；</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>断网后组内重新选主；恢复网络后查看是否从新的主节点同步数据，数据完整且跟新主数据一致；删除成功，数据不存在；删除失败，数据存在，且可正常查询；</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>remove/truncate</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>upsert/update</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>聚集组合方式</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>闪断2s、9s，超过7S后重新选主</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>主子表</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>dataRG主节点所在服务器CPU耗尽</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>dataRG备节点所在服务器CPU耗尽</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>dataRG主节点所在服务器内存耗尽</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>dataRG备节点所在服务器内存耗尽</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>主节点操作成功，故障恢复后和主节点数据一致</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>catalog主节点所在服务器CPU耗尽</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>catalog备节点所在服务器CPU耗尽</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>catalog主节点所在服务器内存耗尽</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>catalog备节点所在服务器内存耗尽</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>catalog主节点正常重启</t>
-  </si>
-  <si>
-    <t>catalog备节点正常重启</t>
-  </si>
-  <si>
-    <t>dataRG主节点正常重启</t>
-  </si>
-  <si>
-    <t>catalog备节点异常重启</t>
-  </si>
-  <si>
-    <t>dataRG主节点异常重启</t>
-  </si>
-  <si>
-    <t>catalog主节点异常重启</t>
-  </si>
-  <si>
-    <t>catalog备节点异常重启</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>catalog主节点异常重启</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>网络单通（低优先级）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>umount盘（低优先级）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>磁盘损坏（低优先级）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>dataRG连续降备</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>重复一种异常</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>几种异常组合（数据恢复过程中异常）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>基本操作</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>断网后组内重新选主；恢复网络后查看是否从新的主节点同步数据，数据完整且跟新主数据一致；挂载成功在对应主表做基本操作成功(如insert数据)；</t>
-  </si>
-  <si>
-    <t>断网后组内连续降备选主；恢复网络后查看是否从新的主节点同步数据；挂载成功在对应主表做基本操作成功(如insert数据)；主表catalog数据完整且一致；</t>
-  </si>
-  <si>
-    <t>重启后组内重新选主；恢复后查看是否从新的主节点同步数据，数据完整且跟新主数据一致；挂载成功在对应主表做基本操作成功(如insert数据)；</t>
-  </si>
-  <si>
-    <t>断网后组内重新选主；恢复网络后查看是否从新的主节点同步数据，数据完整且跟新主数据一致；子表挂载成功在对应主表做基本操作成功(如insert数据)；挂载失败在该普通表做基本操作成功</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>断网后组内重新选主；恢复网络后查看是否从新的主节点同步数据，数据完整且跟新主数据一致；分离成功在该普通主表做基本操作成功(如insert数据)；</t>
   </si>
   <si>
     <r>
@@ -1377,6 +1321,22 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>dataRG备节点断网</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>detachCL</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>在主表insert大量数据</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>主表range，子表range，多分区键，在主表insert</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <r>
       <t>断网后组内重新选主；恢复网络后查看是否从新的主节点同步数据，数据完整且跟新主数据一致；insert成功，数据完整，可正常查询；</t>
     </r>
@@ -1396,7 +1356,15 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>catalog备节点断网</t>
+    <t>主表range，子表hash，AutoSplit：true,多个分区键，在主表insert</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>断网后组内重新选主；恢复网络后查看是否从新的主节点同步数据，数据完整且跟新主数据一致；insert成功，数据完整，可正常查询；insert失败数据丢失，不存在垃圾数据；</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>主表range，子表hash，AutoSplit：false,在主表remove</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -1419,23 +1387,43 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>在主表upsert大量数据</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>upsert/update</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>断网后组内重新选主；恢复网络后查看是否从新的主节点同步数据，数据完整且跟新主数据一致；upsert成功，数据被更新；</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>dataRG主节点断网</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>dataRG备节点断网</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>dataRG连续降备</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>断网后组内重新选主；恢复网络后查看是否从新的主节点同步数据，数据完整且跟新主数据一致；aggregate成功，返回结果正确；aggregate失败正常报错，网络恢复后可以继续查询；</t>
+    <t>断网后组内连续降备选主；恢复网络后查看是否从新的主节点同步数据；upsert成功，数据被更新；upsert失败数据不被更新，数据正常存在；</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>在主表remove大量数据</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>remove/truncate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>断网后组内重新选主；恢复网络后查看是否从新的主节点同步数据，数据完整且跟新主数据一致；删除成功，数据不存在；删除失败，数据存在，且可正常查询；</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>在主表做aggregate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>聚集组合方式</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>网络闪断</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -1443,56 +1431,44 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>dataRG主节点网络闪断</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>dataRG备节点网络闪断</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>catalog主节点网络闪断</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>dataRG备节点网络闪断</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>catalog备节点网络闪断</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>catalog备节点网络闪断</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>dataRG主节点网络闪断</t>
+    <t>闪断2s、9s，超过7S后重新选主</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>网络拥塞</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>catalog主节点网络拥塞</t>
-  </si>
-  <si>
-    <t>catalog主节点网络拥塞</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>dataRG备节点网络拥塞</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>catalog备节点网络拥塞</t>
-  </si>
-  <si>
-    <t>dataRG主节点网络拥塞</t>
-  </si>
-  <si>
-    <t>catalog主节点网络拥塞</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>insert/upsert/remove</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、普通拥塞
+2、时间设置超过9s延迟</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CPU耗尽</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>catalog主节点所在服务器CPU耗尽</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>故障恢复后数据没有丢失，重新操作成功</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>catalog备节点所在服务器CPU耗尽</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>主节点操作成功，故障恢复后和主节点数据一致</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>基本操作</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -1501,7 +1477,27 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>detachCL</t>
+    <t>内存耗尽</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>catalog主节点所在服务器内存耗尽</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>catalog备节点所在服务器内存耗尽</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>dataRG主节点所在服务器内存耗尽</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>dataRG备节点所在服务器内存耗尽</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>时间跳变</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -1509,11 +1505,11 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>重复detachCL多次，catalog主节点的时间跳变</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>正常操作过程中时间改变</t>
+    <t>时间跳变后catalog数据不丢失，各节点数据完整一致；attachCL成功，对主表做基本操作，操作成功；</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>时间跳变后catalog数据不丢失，各节点数据完整一致；detachCL成功，对普通表做基本操作，操作成功；</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -1521,27 +1517,19 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>dataRG备节点时间跳变</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>时间跳变后catalog数据不丢失，各节点数据完整一致；attachCL成功，对主表做基本操作，操作成功；</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>时间跳变后catalog数据不丢失，各节点数据完整一致；detachCL成功，对普通表做基本操作，操作成功；</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>时间跳变后dataRG数据不丢失，各节点数据完整一致；基本操作成功，数据查询结果正确；</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>attachCL成功，各节点数据完整一致；</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>attachCL成功，各节点数据完整一致；</t>
+    <t>大压力高并发</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>对同一个主表并发attach多个子表</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>取典型值，执行过程中随机取值</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>attachCL的同时detachCL</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -1549,7 +1537,31 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>操作成功，各节点数据完整一致；</t>
+    <t>insert/upsert/remove组合并发操作</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>磁盘满</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>catalog主节点所在服务器磁盘满</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>恢复故障后查看主节点数据完整，故障恢复后主节点；挂载成功在对应主表做基本操作成功(如insert数据)；</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>catalog主节点备节点所在服务器磁盘满</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>dataRG主节点所在服务器磁盘满</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>节点正常重启</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -1557,99 +1569,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>catalog主节点所在服务器磁盘满</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>catalog主节点备节点所在服务器磁盘满</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>attachCL</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>attachCL</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>基本操作</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>测试项</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>在主表insert大量数据</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>在主表upsert大量数据</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>在主表remove大量数据</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>在主表做aggregate</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>插入16M大小的数据</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>createDomain</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>对同一个主表并发attach多个子表</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>对不同主表并发attach多个子表</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>attachCL的同时detachCL</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>insert/upsert/remove组合并发操作</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>catalog主节点所在服务器磁盘满</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>dataRG主节点所在服务器磁盘满</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>dataRG备节点所在服务器磁盘满</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>恢复故障后查看主节点数据完整，故障恢复后主节点；挂载成功在对应主表做基本操作成功(如insert数据)；</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>catalog备节点正常重启</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>dataRG备节点正常重启</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>catalog备节点正常重启</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>dataRG主节点正常重启（基本操作考虑（余婷））</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -1663,11 +1583,31 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>dataRG主节点正常重启</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>insert/upsert/remove
 主表range，子表hash，AutoSplit：false,在主表remove</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>dataRG主节点正常重启（基本操作考虑（余婷））</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>节点异常重启</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>catalog主节点异常重启</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>catalog备节点异常重启</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>dataRG主节点异常重启</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1676,7 +1616,23 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>dataRG主节点正常重启</t>
+    <t>主机正常重启</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>主机异常重启</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>同节点异常重启</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ulimit配置异常(堆栈、句柄、线程数、虚存)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>重复一种异常</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -1684,43 +1640,27 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>组合异常(包括同一异常多次出现)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>catalog主节点XX异常</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>恢复故障后，主备节点数据一致</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>次数取值？随机值</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>catalog备节点XX异常</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>dataRG主节点XX异常</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>主节点所在主机异常重启</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>备节点所在主机异常重启</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>同节点正常重启</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>同节点异常重启</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>等友滨确认后再考虑具体测试点</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>dataRG备节点XX异常</t>
+    <t>几种异常组合（数据恢复过程中异常）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>不影响操作，故障恢复后数据一致</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -1728,31 +1668,15 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>coord与catalog网络单通</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>coord与dataRG网络单通</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>catalog与dataRG网络单通</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>coord与coord网络单通</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>catalog与catalog网络单通</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>dataRG与dataRG网络单通</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>coord、catelog、dataRG之间网络单通</t>
+    <t>catalog主节点跟其他catalog备节点网络单通</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>umount盘（低优先级）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>磁盘损坏（低优先级）</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2238,7 +2162,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G158"/>
+  <dimension ref="A1:G154"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="9.875" style="6" customWidth="1"/>
@@ -2253,43 +2177,43 @@
   <sheetData>
     <row r="1" spans="1:7" s="3" customFormat="1" ht="27">
       <c r="A1" s="1" t="s">
-        <v>7</v>
+        <v>46</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>8</v>
+        <v>47</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>118</v>
+        <v>48</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>9</v>
+        <v>49</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>11</v>
+        <v>51</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>12</v>
+        <v>52</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="40.5">
       <c r="A2" s="4" t="s">
-        <v>1</v>
+        <v>53</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>13</v>
+        <v>54</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>115</v>
+        <v>55</v>
       </c>
       <c r="D2" s="4"/>
       <c r="E2" s="4" t="s">
-        <v>14</v>
+        <v>56</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>69</v>
+        <v>11</v>
       </c>
       <c r="G2" s="4"/>
     </row>
@@ -2299,10 +2223,10 @@
       <c r="C3" s="8"/>
       <c r="D3" s="7"/>
       <c r="E3" s="7" t="s">
-        <v>15</v>
+        <v>57</v>
       </c>
       <c r="F3" s="7" t="s">
-        <v>16</v>
+        <v>58</v>
       </c>
       <c r="G3" s="7"/>
     </row>
@@ -2312,10 +2236,10 @@
       <c r="C4" s="8"/>
       <c r="D4" s="7"/>
       <c r="E4" s="7" t="s">
-        <v>79</v>
+        <v>59</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>72</v>
+        <v>41</v>
       </c>
       <c r="G4" s="7"/>
     </row>
@@ -2325,10 +2249,10 @@
       <c r="C5" s="8"/>
       <c r="D5" s="7"/>
       <c r="E5" s="7" t="s">
-        <v>18</v>
+        <v>60</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>74</v>
+        <v>61</v>
       </c>
       <c r="G5" s="7"/>
     </row>
@@ -2338,10 +2262,10 @@
       <c r="C6" s="8"/>
       <c r="D6" s="7"/>
       <c r="E6" s="7" t="s">
-        <v>80</v>
+        <v>62</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>16</v>
+        <v>58</v>
       </c>
       <c r="G6" s="7"/>
     </row>
@@ -2349,14 +2273,14 @@
       <c r="A7" s="7"/>
       <c r="B7" s="7"/>
       <c r="C7" s="8" t="s">
-        <v>99</v>
+        <v>63</v>
       </c>
       <c r="D7" s="7"/>
       <c r="E7" s="7" t="s">
-        <v>20</v>
+        <v>56</v>
       </c>
       <c r="F7" s="7" t="s">
-        <v>73</v>
+        <v>14</v>
       </c>
       <c r="G7" s="7"/>
     </row>
@@ -2366,10 +2290,10 @@
       <c r="C8" s="8"/>
       <c r="D8" s="7"/>
       <c r="E8" s="7" t="s">
-        <v>15</v>
+        <v>57</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>16</v>
+        <v>58</v>
       </c>
       <c r="G8" s="7"/>
     </row>
@@ -2379,10 +2303,10 @@
       <c r="C9" s="8"/>
       <c r="D9" s="7"/>
       <c r="E9" s="7" t="s">
-        <v>17</v>
+        <v>59</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>73</v>
+        <v>14</v>
       </c>
       <c r="G9" s="7"/>
     </row>
@@ -2392,10 +2316,10 @@
       <c r="C10" s="8"/>
       <c r="D10" s="7"/>
       <c r="E10" s="7" t="s">
-        <v>18</v>
+        <v>60</v>
       </c>
       <c r="F10" s="7" t="s">
-        <v>70</v>
+        <v>12</v>
       </c>
       <c r="G10" s="7"/>
     </row>
@@ -2405,10 +2329,10 @@
       <c r="C11" s="8"/>
       <c r="D11" s="7"/>
       <c r="E11" s="7" t="s">
-        <v>80</v>
+        <v>62</v>
       </c>
       <c r="F11" s="7" t="s">
-        <v>16</v>
+        <v>58</v>
       </c>
       <c r="G11" s="7"/>
     </row>
@@ -2416,16 +2340,16 @@
       <c r="A12" s="7"/>
       <c r="B12" s="7"/>
       <c r="C12" s="8" t="s">
-        <v>119</v>
+        <v>64</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>21</v>
+        <v>65</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>20</v>
+        <v>56</v>
       </c>
       <c r="F12" s="7" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="G12" s="7"/>
     </row>
@@ -2435,7 +2359,7 @@
       <c r="C13" s="8"/>
       <c r="D13" s="7"/>
       <c r="E13" s="11" t="s">
-        <v>76</v>
+        <v>57</v>
       </c>
       <c r="F13" s="7"/>
       <c r="G13" s="7"/>
@@ -2445,13 +2369,13 @@
       <c r="B14" s="7"/>
       <c r="C14" s="8"/>
       <c r="D14" s="7" t="s">
-        <v>36</v>
+        <v>67</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>17</v>
+        <v>59</v>
       </c>
       <c r="F14" s="7" t="s">
-        <v>6</v>
+        <v>68</v>
       </c>
       <c r="G14" s="7"/>
     </row>
@@ -2460,13 +2384,13 @@
       <c r="B15" s="7"/>
       <c r="C15" s="8"/>
       <c r="D15" s="7" t="s">
-        <v>37</v>
+        <v>69</v>
       </c>
       <c r="E15" s="7" t="s">
-        <v>18</v>
+        <v>60</v>
       </c>
       <c r="F15" s="7" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="G15" s="7"/>
     </row>
@@ -2476,10 +2400,10 @@
       <c r="C16" s="8"/>
       <c r="D16" s="7"/>
       <c r="E16" s="7" t="s">
-        <v>80</v>
+        <v>62</v>
       </c>
       <c r="F16" s="7" t="s">
-        <v>16</v>
+        <v>58</v>
       </c>
       <c r="G16" s="7"/>
     </row>
@@ -2487,16 +2411,16 @@
       <c r="A17" s="7"/>
       <c r="B17" s="7"/>
       <c r="C17" s="8" t="s">
-        <v>120</v>
+        <v>71</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>41</v>
+        <v>72</v>
       </c>
       <c r="E17" s="7" t="s">
-        <v>17</v>
+        <v>59</v>
       </c>
       <c r="F17" s="7" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="G17" s="7"/>
     </row>
@@ -2506,10 +2430,10 @@
       <c r="C18" s="8"/>
       <c r="D18" s="7"/>
       <c r="E18" s="7" t="s">
-        <v>18</v>
+        <v>60</v>
       </c>
       <c r="F18" s="7" t="s">
-        <v>38</v>
+        <v>74</v>
       </c>
       <c r="G18" s="7"/>
     </row>
@@ -2519,10 +2443,10 @@
       <c r="C19" s="8"/>
       <c r="D19" s="7"/>
       <c r="E19" s="7" t="s">
-        <v>80</v>
+        <v>62</v>
       </c>
       <c r="F19" s="7" t="s">
-        <v>16</v>
+        <v>58</v>
       </c>
       <c r="G19" s="7"/>
     </row>
@@ -2530,16 +2454,16 @@
       <c r="A20" s="7"/>
       <c r="B20" s="7"/>
       <c r="C20" s="8" t="s">
-        <v>121</v>
+        <v>75</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>40</v>
+        <v>76</v>
       </c>
       <c r="E20" s="7" t="s">
-        <v>5</v>
+        <v>59</v>
       </c>
       <c r="F20" s="7" t="s">
-        <v>39</v>
+        <v>77</v>
       </c>
       <c r="G20" s="7"/>
     </row>
@@ -2549,10 +2473,10 @@
       <c r="C21" s="8"/>
       <c r="D21" s="7"/>
       <c r="E21" s="7" t="s">
-        <v>80</v>
+        <v>62</v>
       </c>
       <c r="F21" s="7" t="s">
-        <v>16</v>
+        <v>58</v>
       </c>
       <c r="G21" s="7"/>
     </row>
@@ -2560,16 +2484,16 @@
       <c r="A22" s="7"/>
       <c r="B22" s="7"/>
       <c r="C22" s="8" t="s">
-        <v>122</v>
+        <v>78</v>
       </c>
       <c r="D22" s="7" t="s">
-        <v>42</v>
+        <v>79</v>
       </c>
       <c r="E22" s="7" t="s">
-        <v>5</v>
+        <v>59</v>
       </c>
       <c r="F22" s="7" t="s">
-        <v>82</v>
+        <v>15</v>
       </c>
       <c r="G22" s="7"/>
     </row>
@@ -2577,36 +2501,36 @@
       <c r="A23" s="7"/>
       <c r="B23" s="7"/>
       <c r="C23" s="8" t="s">
-        <v>123</v>
+        <v>30</v>
       </c>
       <c r="D23" s="7"/>
       <c r="E23" s="7" t="s">
-        <v>5</v>
+        <v>59</v>
       </c>
       <c r="F23" s="7" t="s">
-        <v>6</v>
+        <v>68</v>
       </c>
       <c r="G23" s="7"/>
     </row>
-    <row r="24" spans="1:7" ht="40.5">
+    <row r="24" spans="1:7" ht="54">
       <c r="A24" s="4" t="s">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>13</v>
+        <v>54</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>115</v>
+        <v>55</v>
       </c>
       <c r="D24" s="4"/>
       <c r="E24" s="4" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="F24" s="4" t="s">
-        <v>69</v>
+        <v>44</v>
       </c>
       <c r="G24" s="4" t="s">
-        <v>43</v>
+        <v>82</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -2615,10 +2539,10 @@
       <c r="C25" s="8"/>
       <c r="D25" s="7"/>
       <c r="E25" s="7" t="s">
-        <v>84</v>
+        <v>18</v>
       </c>
       <c r="F25" s="7" t="s">
-        <v>16</v>
+        <v>58</v>
       </c>
       <c r="G25" s="7"/>
     </row>
@@ -2628,7 +2552,7 @@
       <c r="C26" s="8"/>
       <c r="D26" s="7"/>
       <c r="E26" s="7" t="s">
-        <v>18</v>
+        <v>60</v>
       </c>
       <c r="F26" s="7"/>
       <c r="G26" s="7"/>
@@ -2639,7 +2563,7 @@
       <c r="C27" s="8"/>
       <c r="D27" s="7"/>
       <c r="E27" s="7" t="s">
-        <v>87</v>
+        <v>16</v>
       </c>
       <c r="F27" s="7"/>
       <c r="G27" s="7"/>
@@ -2650,7 +2574,7 @@
       <c r="C28" s="8"/>
       <c r="D28" s="7"/>
       <c r="E28" s="7" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="F28" s="7"/>
       <c r="G28" s="7"/>
@@ -2659,11 +2583,11 @@
       <c r="A29" s="7"/>
       <c r="B29" s="7"/>
       <c r="C29" s="8" t="s">
-        <v>99</v>
+        <v>63</v>
       </c>
       <c r="D29" s="7"/>
       <c r="E29" s="7" t="s">
-        <v>88</v>
+        <v>17</v>
       </c>
       <c r="F29" s="7"/>
       <c r="G29" s="7"/>
@@ -2674,7 +2598,7 @@
       <c r="C30" s="8"/>
       <c r="D30" s="7"/>
       <c r="E30" s="7" t="s">
-        <v>84</v>
+        <v>18</v>
       </c>
       <c r="F30" s="7"/>
       <c r="G30" s="7"/>
@@ -2685,7 +2609,7 @@
       <c r="C31" s="8"/>
       <c r="D31" s="7"/>
       <c r="E31" s="7" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="F31" s="7"/>
       <c r="G31" s="7"/>
@@ -2696,7 +2620,7 @@
       <c r="C32" s="8"/>
       <c r="D32" s="7"/>
       <c r="E32" s="7" t="s">
-        <v>85</v>
+        <v>16</v>
       </c>
       <c r="F32" s="7"/>
       <c r="G32" s="7"/>
@@ -2707,7 +2631,7 @@
       <c r="C33" s="8"/>
       <c r="D33" s="7"/>
       <c r="E33" s="7" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="F33" s="7"/>
       <c r="G33" s="7"/>
@@ -2716,13 +2640,13 @@
       <c r="A34" s="7"/>
       <c r="B34" s="7"/>
       <c r="C34" s="8" t="s">
-        <v>119</v>
+        <v>64</v>
       </c>
       <c r="D34" s="7" t="s">
-        <v>21</v>
+        <v>65</v>
       </c>
       <c r="E34" s="7" t="s">
-        <v>89</v>
+        <v>17</v>
       </c>
       <c r="F34" s="7"/>
       <c r="G34" s="7"/>
@@ -2733,7 +2657,7 @@
       <c r="C35" s="8"/>
       <c r="D35" s="7"/>
       <c r="E35" s="7" t="s">
-        <v>84</v>
+        <v>18</v>
       </c>
       <c r="F35" s="7"/>
       <c r="G35" s="7"/>
@@ -2743,10 +2667,10 @@
       <c r="B36" s="7"/>
       <c r="C36" s="8"/>
       <c r="D36" s="7" t="s">
-        <v>36</v>
+        <v>67</v>
       </c>
       <c r="E36" s="12" t="s">
-        <v>81</v>
+        <v>60</v>
       </c>
       <c r="F36" s="7"/>
       <c r="G36" s="7"/>
@@ -2756,10 +2680,10 @@
       <c r="B37" s="7"/>
       <c r="C37" s="8"/>
       <c r="D37" s="7" t="s">
-        <v>37</v>
+        <v>69</v>
       </c>
       <c r="E37" s="7" t="s">
-        <v>85</v>
+        <v>16</v>
       </c>
       <c r="F37" s="7"/>
       <c r="G37" s="7"/>
@@ -2768,13 +2692,13 @@
       <c r="A38" s="7"/>
       <c r="B38" s="7"/>
       <c r="C38" s="8" t="s">
-        <v>120</v>
+        <v>71</v>
       </c>
       <c r="D38" s="7" t="s">
-        <v>41</v>
+        <v>72</v>
       </c>
       <c r="E38" s="7" t="s">
-        <v>84</v>
+        <v>18</v>
       </c>
       <c r="F38" s="7"/>
       <c r="G38" s="7"/>
@@ -2785,7 +2709,7 @@
       <c r="C39" s="8"/>
       <c r="D39" s="7"/>
       <c r="E39" s="7" t="s">
-        <v>85</v>
+        <v>16</v>
       </c>
       <c r="F39" s="7"/>
       <c r="G39" s="7"/>
@@ -2794,13 +2718,13 @@
       <c r="A40" s="7"/>
       <c r="B40" s="7"/>
       <c r="C40" s="8" t="s">
-        <v>121</v>
+        <v>75</v>
       </c>
       <c r="D40" s="7" t="s">
-        <v>40</v>
+        <v>76</v>
       </c>
       <c r="E40" s="7" t="s">
-        <v>84</v>
+        <v>18</v>
       </c>
       <c r="F40" s="7"/>
       <c r="G40" s="7"/>
@@ -2811,7 +2735,7 @@
       <c r="C41" s="8"/>
       <c r="D41" s="7"/>
       <c r="E41" s="7" t="s">
-        <v>85</v>
+        <v>16</v>
       </c>
       <c r="F41" s="7"/>
       <c r="G41" s="7"/>
@@ -2820,13 +2744,13 @@
       <c r="A42" s="7"/>
       <c r="B42" s="7"/>
       <c r="C42" s="8" t="s">
-        <v>122</v>
+        <v>78</v>
       </c>
       <c r="D42" s="7" t="s">
-        <v>42</v>
+        <v>79</v>
       </c>
       <c r="E42" s="7" t="s">
-        <v>84</v>
+        <v>18</v>
       </c>
       <c r="F42" s="7"/>
       <c r="G42" s="7"/>
@@ -2835,34 +2759,34 @@
       <c r="A43" s="7"/>
       <c r="B43" s="7"/>
       <c r="C43" s="8" t="s">
-        <v>123</v>
+        <v>30</v>
       </c>
       <c r="D43" s="7"/>
       <c r="E43" s="7" t="s">
-        <v>90</v>
+        <v>18</v>
       </c>
       <c r="F43" s="7"/>
       <c r="G43" s="7"/>
     </row>
     <row r="44" spans="1:7" ht="40.5">
       <c r="A44" s="4" t="s">
-        <v>3</v>
+        <v>83</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>13</v>
+        <v>54</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>115</v>
+        <v>55</v>
       </c>
       <c r="D44" s="4"/>
       <c r="E44" s="4" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="F44" s="4" t="s">
-        <v>69</v>
+        <v>45</v>
       </c>
       <c r="G44" s="4" t="s">
-        <v>0</v>
+        <v>85</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -2871,10 +2795,10 @@
       <c r="C45" s="8"/>
       <c r="D45" s="7"/>
       <c r="E45" s="7" t="s">
-        <v>94</v>
+        <v>21</v>
       </c>
       <c r="F45" s="7" t="s">
-        <v>16</v>
+        <v>58</v>
       </c>
       <c r="G45" s="7"/>
     </row>
@@ -2884,7 +2808,7 @@
       <c r="C46" s="8"/>
       <c r="D46" s="7"/>
       <c r="E46" s="7" t="s">
-        <v>95</v>
+        <v>22</v>
       </c>
       <c r="F46" s="7"/>
       <c r="G46" s="7"/>
@@ -2895,7 +2819,7 @@
       <c r="C47" s="8"/>
       <c r="D47" s="7"/>
       <c r="E47" s="7" t="s">
-        <v>18</v>
+        <v>60</v>
       </c>
       <c r="F47" s="7"/>
       <c r="G47" s="7"/>
@@ -2906,7 +2830,7 @@
       <c r="C48" s="8"/>
       <c r="D48" s="7"/>
       <c r="E48" s="12" t="s">
-        <v>93</v>
+        <v>20</v>
       </c>
       <c r="F48" s="7"/>
       <c r="G48" s="7"/>
@@ -2915,11 +2839,11 @@
       <c r="A49" s="7"/>
       <c r="B49" s="7"/>
       <c r="C49" s="8" t="s">
-        <v>99</v>
+        <v>63</v>
       </c>
       <c r="D49" s="7"/>
       <c r="E49" s="7" t="s">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="F49" s="7"/>
       <c r="G49" s="7"/>
@@ -2930,7 +2854,7 @@
       <c r="C50" s="8"/>
       <c r="D50" s="7"/>
       <c r="E50" s="7" t="s">
-        <v>94</v>
+        <v>21</v>
       </c>
       <c r="F50" s="7"/>
       <c r="G50" s="7"/>
@@ -2941,7 +2865,7 @@
       <c r="C51" s="8"/>
       <c r="D51" s="7"/>
       <c r="E51" s="7" t="s">
-        <v>95</v>
+        <v>22</v>
       </c>
       <c r="F51" s="7"/>
       <c r="G51" s="7"/>
@@ -2952,7 +2876,7 @@
       <c r="C52" s="8"/>
       <c r="D52" s="7"/>
       <c r="E52" s="7" t="s">
-        <v>18</v>
+        <v>60</v>
       </c>
       <c r="F52" s="7"/>
       <c r="G52" s="7"/>
@@ -2961,13 +2885,13 @@
       <c r="A53" s="7"/>
       <c r="B53" s="7"/>
       <c r="C53" s="8" t="s">
-        <v>119</v>
+        <v>64</v>
       </c>
       <c r="D53" s="7" t="s">
-        <v>21</v>
+        <v>65</v>
       </c>
       <c r="E53" s="7" t="s">
-        <v>91</v>
+        <v>19</v>
       </c>
       <c r="F53" s="7"/>
       <c r="G53" s="7"/>
@@ -2977,10 +2901,10 @@
       <c r="B54" s="7"/>
       <c r="C54" s="8"/>
       <c r="D54" s="7" t="s">
-        <v>36</v>
+        <v>67</v>
       </c>
       <c r="E54" s="7" t="s">
-        <v>95</v>
+        <v>22</v>
       </c>
       <c r="F54" s="7"/>
       <c r="G54" s="7"/>
@@ -2990,10 +2914,10 @@
       <c r="B55" s="7"/>
       <c r="C55" s="8"/>
       <c r="D55" s="7" t="s">
-        <v>37</v>
+        <v>69</v>
       </c>
       <c r="E55" s="7" t="s">
-        <v>18</v>
+        <v>60</v>
       </c>
       <c r="F55" s="7"/>
       <c r="G55" s="7"/>
@@ -3004,7 +2928,7 @@
       <c r="C56" s="8"/>
       <c r="D56" s="7"/>
       <c r="E56" s="7" t="s">
-        <v>93</v>
+        <v>20</v>
       </c>
       <c r="F56" s="7"/>
       <c r="G56" s="7"/>
@@ -3013,13 +2937,13 @@
       <c r="A57" s="7"/>
       <c r="B57" s="7"/>
       <c r="C57" s="8" t="s">
-        <v>120</v>
+        <v>71</v>
       </c>
       <c r="D57" s="7" t="s">
-        <v>41</v>
+        <v>72</v>
       </c>
       <c r="E57" s="7" t="s">
-        <v>95</v>
+        <v>22</v>
       </c>
       <c r="F57" s="7"/>
       <c r="G57" s="7"/>
@@ -3030,7 +2954,7 @@
       <c r="C58" s="8"/>
       <c r="D58" s="7"/>
       <c r="E58" s="12" t="s">
-        <v>81</v>
+        <v>60</v>
       </c>
       <c r="F58" s="7"/>
       <c r="G58" s="7"/>
@@ -3041,7 +2965,7 @@
       <c r="C59" s="8"/>
       <c r="D59" s="7"/>
       <c r="E59" s="7" t="s">
-        <v>93</v>
+        <v>20</v>
       </c>
       <c r="F59" s="7"/>
       <c r="G59" s="7"/>
@@ -3050,13 +2974,13 @@
       <c r="A60" s="7"/>
       <c r="B60" s="7"/>
       <c r="C60" s="8" t="s">
-        <v>121</v>
+        <v>75</v>
       </c>
       <c r="D60" s="7" t="s">
-        <v>40</v>
+        <v>76</v>
       </c>
       <c r="E60" s="7" t="s">
-        <v>95</v>
+        <v>22</v>
       </c>
       <c r="F60" s="7"/>
       <c r="G60" s="7"/>
@@ -3067,7 +2991,7 @@
       <c r="C61" s="8"/>
       <c r="D61" s="7"/>
       <c r="E61" s="7" t="s">
-        <v>93</v>
+        <v>20</v>
       </c>
       <c r="F61" s="7"/>
       <c r="G61" s="7"/>
@@ -3076,13 +3000,13 @@
       <c r="A62" s="7"/>
       <c r="B62" s="7"/>
       <c r="C62" s="8" t="s">
-        <v>122</v>
+        <v>78</v>
       </c>
       <c r="D62" s="7" t="s">
-        <v>42</v>
+        <v>79</v>
       </c>
       <c r="E62" s="7" t="s">
-        <v>95</v>
+        <v>22</v>
       </c>
       <c r="F62" s="7"/>
       <c r="G62" s="7"/>
@@ -3091,11 +3015,11 @@
       <c r="A63" s="7"/>
       <c r="B63" s="7"/>
       <c r="C63" s="8" t="s">
-        <v>123</v>
+        <v>30</v>
       </c>
       <c r="D63" s="7"/>
       <c r="E63" s="7" t="s">
-        <v>95</v>
+        <v>22</v>
       </c>
       <c r="F63" s="7"/>
       <c r="G63" s="7"/>
@@ -3111,20 +3035,20 @@
     </row>
     <row r="65" spans="1:7" ht="27">
       <c r="A65" s="4" t="s">
-        <v>22</v>
+        <v>86</v>
       </c>
       <c r="B65" s="4" t="s">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="C65" s="5" t="s">
-        <v>115</v>
+        <v>55</v>
       </c>
       <c r="D65" s="4"/>
       <c r="E65" s="4" t="s">
-        <v>50</v>
+        <v>87</v>
       </c>
       <c r="F65" s="4" t="s">
-        <v>23</v>
+        <v>88</v>
       </c>
       <c r="G65" s="4"/>
     </row>
@@ -3134,10 +3058,10 @@
       <c r="C66" s="8"/>
       <c r="D66" s="7"/>
       <c r="E66" s="7" t="s">
-        <v>51</v>
+        <v>89</v>
       </c>
       <c r="F66" s="7" t="s">
-        <v>49</v>
+        <v>90</v>
       </c>
       <c r="G66" s="7"/>
     </row>
@@ -3147,7 +3071,7 @@
       <c r="C67" s="8"/>
       <c r="D67" s="7"/>
       <c r="E67" s="7" t="s">
-        <v>45</v>
+        <v>2</v>
       </c>
       <c r="F67" s="7"/>
       <c r="G67" s="7"/>
@@ -3156,11 +3080,11 @@
       <c r="A68" s="7"/>
       <c r="B68" s="7"/>
       <c r="C68" s="8" t="s">
-        <v>99</v>
+        <v>63</v>
       </c>
       <c r="D68" s="7"/>
       <c r="E68" s="7" t="s">
-        <v>45</v>
+        <v>2</v>
       </c>
       <c r="F68" s="7"/>
       <c r="G68" s="7"/>
@@ -3169,13 +3093,13 @@
       <c r="A69" s="7"/>
       <c r="B69" s="7"/>
       <c r="C69" s="8" t="s">
-        <v>117</v>
+        <v>91</v>
       </c>
       <c r="D69" s="7" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="E69" s="7" t="s">
-        <v>45</v>
+        <v>2</v>
       </c>
       <c r="F69" s="7"/>
       <c r="G69" s="7"/>
@@ -3186,27 +3110,27 @@
       <c r="C70" s="8"/>
       <c r="D70" s="7"/>
       <c r="E70" s="7" t="s">
-        <v>46</v>
+        <v>3</v>
       </c>
       <c r="F70" s="7"/>
       <c r="G70" s="7"/>
     </row>
     <row r="71" spans="1:7" ht="27">
       <c r="A71" s="4" t="s">
-        <v>24</v>
+        <v>93</v>
       </c>
       <c r="B71" s="4" t="s">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="C71" s="5" t="s">
-        <v>115</v>
+        <v>55</v>
       </c>
       <c r="D71" s="4"/>
       <c r="E71" s="4" t="s">
-        <v>52</v>
+        <v>94</v>
       </c>
       <c r="F71" s="4" t="s">
-        <v>23</v>
+        <v>88</v>
       </c>
       <c r="G71" s="4"/>
     </row>
@@ -3216,10 +3140,10 @@
       <c r="C72" s="8"/>
       <c r="D72" s="7"/>
       <c r="E72" s="7" t="s">
-        <v>53</v>
+        <v>95</v>
       </c>
       <c r="F72" s="7" t="s">
-        <v>49</v>
+        <v>90</v>
       </c>
       <c r="G72" s="7"/>
     </row>
@@ -3229,7 +3153,7 @@
       <c r="C73" s="8"/>
       <c r="D73" s="7"/>
       <c r="E73" s="7" t="s">
-        <v>47</v>
+        <v>96</v>
       </c>
       <c r="F73" s="7"/>
       <c r="G73" s="7"/>
@@ -3238,11 +3162,11 @@
       <c r="A74" s="7"/>
       <c r="B74" s="7"/>
       <c r="C74" s="8" t="s">
-        <v>99</v>
+        <v>63</v>
       </c>
       <c r="D74" s="7"/>
       <c r="E74" s="7" t="s">
-        <v>47</v>
+        <v>96</v>
       </c>
       <c r="F74" s="7"/>
       <c r="G74" s="7"/>
@@ -3251,13 +3175,13 @@
       <c r="A75" s="7"/>
       <c r="B75" s="7"/>
       <c r="C75" s="8" t="s">
-        <v>117</v>
+        <v>91</v>
       </c>
       <c r="D75" s="7" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="E75" s="7" t="s">
-        <v>47</v>
+        <v>96</v>
       </c>
       <c r="F75" s="7"/>
       <c r="G75" s="7"/>
@@ -3268,44 +3192,44 @@
       <c r="C76" s="8"/>
       <c r="D76" s="7"/>
       <c r="E76" s="7" t="s">
-        <v>48</v>
+        <v>97</v>
       </c>
       <c r="F76" s="7"/>
       <c r="G76" s="7"/>
     </row>
     <row r="77" spans="1:7" ht="40.5">
       <c r="A77" s="4" t="s">
-        <v>25</v>
+        <v>98</v>
       </c>
       <c r="B77" s="4" t="s">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="C77" s="5" t="s">
-        <v>115</v>
+        <v>55</v>
       </c>
       <c r="D77" s="4"/>
       <c r="E77" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="F77" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="F77" s="4" t="s">
-        <v>105</v>
-      </c>
       <c r="G77" s="4" t="s">
-        <v>102</v>
+        <v>25</v>
       </c>
     </row>
     <row r="78" spans="1:7" ht="40.5">
       <c r="A78" s="7"/>
       <c r="B78" s="7"/>
       <c r="C78" s="8" t="s">
-        <v>99</v>
+        <v>63</v>
       </c>
       <c r="D78" s="7"/>
       <c r="E78" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="F78" s="7" t="s">
         <v>101</v>
-      </c>
-      <c r="F78" s="7" t="s">
-        <v>106</v>
       </c>
       <c r="G78" s="7"/>
     </row>
@@ -3313,16 +3237,16 @@
       <c r="A79" s="7"/>
       <c r="B79" s="7"/>
       <c r="C79" s="8" t="s">
-        <v>117</v>
+        <v>91</v>
       </c>
       <c r="D79" s="7" t="s">
-        <v>97</v>
+        <v>23</v>
       </c>
       <c r="E79" s="7" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F79" s="7" t="s">
-        <v>107</v>
+        <v>27</v>
       </c>
       <c r="G79" s="7"/>
     </row>
@@ -3332,42 +3256,42 @@
       <c r="C80" s="8"/>
       <c r="D80" s="7"/>
       <c r="E80" s="7" t="s">
-        <v>104</v>
+        <v>26</v>
       </c>
       <c r="F80" s="7" t="s">
-        <v>107</v>
+        <v>27</v>
       </c>
       <c r="G80" s="7"/>
     </row>
     <row r="81" spans="1:7" ht="27">
       <c r="A81" s="4" t="s">
-        <v>26</v>
+        <v>103</v>
       </c>
       <c r="B81" s="4" t="s">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="C81" s="4" t="s">
-        <v>125</v>
+        <v>104</v>
       </c>
       <c r="D81" s="4"/>
       <c r="E81" s="4"/>
       <c r="F81" s="4" t="s">
-        <v>108</v>
+        <v>28</v>
       </c>
       <c r="G81" s="4" t="s">
-        <v>27</v>
+        <v>105</v>
       </c>
     </row>
     <row r="82" spans="1:7" ht="27">
       <c r="A82" s="7"/>
       <c r="B82" s="7"/>
       <c r="C82" s="7" t="s">
-        <v>126</v>
+        <v>31</v>
       </c>
       <c r="D82" s="7"/>
       <c r="E82" s="7"/>
       <c r="F82" s="7" t="s">
-        <v>109</v>
+        <v>28</v>
       </c>
       <c r="G82" s="7"/>
     </row>
@@ -3375,12 +3299,12 @@
       <c r="A83" s="7"/>
       <c r="B83" s="7"/>
       <c r="C83" s="7" t="s">
-        <v>127</v>
+        <v>106</v>
       </c>
       <c r="D83" s="7"/>
       <c r="E83" s="7"/>
       <c r="F83" s="7" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="G83" s="7"/>
     </row>
@@ -3388,31 +3312,31 @@
       <c r="A84" s="7"/>
       <c r="B84" s="7"/>
       <c r="C84" s="7" t="s">
-        <v>128</v>
+        <v>108</v>
       </c>
       <c r="D84" s="7"/>
       <c r="E84" s="7"/>
       <c r="F84" s="7" t="s">
-        <v>111</v>
+        <v>29</v>
       </c>
       <c r="G84" s="7"/>
     </row>
     <row r="85" spans="1:7" ht="27">
       <c r="A85" s="4" t="s">
-        <v>28</v>
+        <v>109</v>
       </c>
       <c r="B85" s="4" t="s">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="C85" s="5" t="s">
-        <v>116</v>
+        <v>55</v>
       </c>
       <c r="D85" s="4"/>
       <c r="E85" s="4" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="F85" s="4" t="s">
-        <v>132</v>
+        <v>111</v>
       </c>
       <c r="G85" s="4"/>
     </row>
@@ -3422,10 +3346,10 @@
       <c r="C86" s="8"/>
       <c r="D86" s="7"/>
       <c r="E86" s="7" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="F86" s="7" t="s">
-        <v>16</v>
+        <v>58</v>
       </c>
       <c r="G86" s="7"/>
     </row>
@@ -3433,11 +3357,11 @@
       <c r="A87" s="7"/>
       <c r="B87" s="7"/>
       <c r="C87" s="8" t="s">
-        <v>99</v>
+        <v>63</v>
       </c>
       <c r="D87" s="7"/>
       <c r="E87" s="7" t="s">
-        <v>129</v>
+        <v>110</v>
       </c>
       <c r="F87" s="7"/>
       <c r="G87" s="7"/>
@@ -3448,7 +3372,7 @@
       <c r="C88" s="8"/>
       <c r="D88" s="7"/>
       <c r="E88" s="7" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="F88" s="7"/>
       <c r="G88" s="7"/>
@@ -3457,13 +3381,13 @@
       <c r="A89" s="7"/>
       <c r="B89" s="7"/>
       <c r="C89" s="8" t="s">
-        <v>68</v>
+        <v>91</v>
       </c>
       <c r="D89" s="7" t="s">
-        <v>97</v>
+        <v>23</v>
       </c>
       <c r="E89" s="7" t="s">
-        <v>130</v>
+        <v>113</v>
       </c>
       <c r="F89" s="7"/>
       <c r="G89" s="7"/>
@@ -3474,27 +3398,27 @@
       <c r="C90" s="8"/>
       <c r="D90" s="7"/>
       <c r="E90" s="7" t="s">
-        <v>131</v>
+        <v>32</v>
       </c>
       <c r="F90" s="7"/>
       <c r="G90" s="7"/>
     </row>
     <row r="91" spans="1:7" ht="40.5">
       <c r="A91" s="4" t="s">
-        <v>29</v>
+        <v>114</v>
       </c>
       <c r="B91" s="4" t="s">
-        <v>13</v>
+        <v>54</v>
       </c>
       <c r="C91" s="5" t="s">
-        <v>115</v>
+        <v>55</v>
       </c>
       <c r="D91" s="4"/>
       <c r="E91" s="4" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="F91" s="4" t="s">
-        <v>71</v>
+        <v>13</v>
       </c>
       <c r="G91" s="4"/>
     </row>
@@ -3504,10 +3428,10 @@
       <c r="C92" s="8"/>
       <c r="D92" s="7"/>
       <c r="E92" s="7" t="s">
-        <v>133</v>
+        <v>116</v>
       </c>
       <c r="F92" s="7" t="s">
-        <v>16</v>
+        <v>58</v>
       </c>
       <c r="G92" s="7"/>
     </row>
@@ -3517,7 +3441,7 @@
       <c r="C93" s="8"/>
       <c r="D93" s="7"/>
       <c r="E93" s="7" t="s">
-        <v>56</v>
+        <v>6</v>
       </c>
       <c r="F93" s="7"/>
       <c r="G93" s="7"/>
@@ -3528,7 +3452,7 @@
       <c r="C94" s="8"/>
       <c r="D94" s="7"/>
       <c r="E94" s="7" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="F94" s="7"/>
       <c r="G94" s="7"/>
@@ -3539,7 +3463,7 @@
       <c r="C95" s="8"/>
       <c r="D95" s="7"/>
       <c r="E95" s="12" t="s">
-        <v>134</v>
+        <v>33</v>
       </c>
       <c r="F95" s="7"/>
       <c r="G95" s="7"/>
@@ -3548,11 +3472,11 @@
       <c r="A96" s="7"/>
       <c r="B96" s="7"/>
       <c r="C96" s="8" t="s">
-        <v>99</v>
+        <v>63</v>
       </c>
       <c r="D96" s="7"/>
       <c r="E96" s="7" t="s">
-        <v>54</v>
+        <v>4</v>
       </c>
       <c r="F96" s="7"/>
       <c r="G96" s="7"/>
@@ -3563,7 +3487,7 @@
       <c r="C97" s="8"/>
       <c r="D97" s="7"/>
       <c r="E97" s="7" t="s">
-        <v>55</v>
+        <v>5</v>
       </c>
       <c r="F97" s="7"/>
       <c r="G97" s="7"/>
@@ -3574,7 +3498,7 @@
       <c r="C98" s="8"/>
       <c r="D98" s="7"/>
       <c r="E98" s="7" t="s">
-        <v>56</v>
+        <v>6</v>
       </c>
       <c r="F98" s="7"/>
       <c r="G98" s="7"/>
@@ -3585,7 +3509,7 @@
       <c r="C99" s="8"/>
       <c r="D99" s="7"/>
       <c r="E99" s="7" t="s">
-        <v>18</v>
+        <v>60</v>
       </c>
       <c r="F99" s="7"/>
       <c r="G99" s="7"/>
@@ -3594,13 +3518,13 @@
       <c r="A100" s="7"/>
       <c r="B100" s="7"/>
       <c r="C100" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="D100" s="7" t="s">
         <v>117</v>
       </c>
-      <c r="D100" s="7" t="s">
-        <v>137</v>
-      </c>
       <c r="E100" s="7" t="s">
-        <v>54</v>
+        <v>4</v>
       </c>
       <c r="F100" s="7"/>
       <c r="G100" s="7"/>
@@ -3611,7 +3535,7 @@
       <c r="C101" s="8"/>
       <c r="D101" s="7"/>
       <c r="E101" s="12" t="s">
-        <v>135</v>
+        <v>116</v>
       </c>
       <c r="F101" s="7"/>
       <c r="G101" s="7"/>
@@ -3621,10 +3545,10 @@
       <c r="B102" s="7"/>
       <c r="C102" s="8"/>
       <c r="D102" s="7" t="s">
-        <v>138</v>
+        <v>118</v>
       </c>
       <c r="E102" s="7" t="s">
-        <v>142</v>
+        <v>119</v>
       </c>
       <c r="F102" s="7"/>
       <c r="G102" s="7"/>
@@ -3634,10 +3558,10 @@
       <c r="B103" s="7"/>
       <c r="C103" s="8"/>
       <c r="D103" s="7" t="s">
-        <v>139</v>
+        <v>120</v>
       </c>
       <c r="E103" s="7" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="F103" s="7"/>
       <c r="G103" s="7"/>
@@ -3648,7 +3572,7 @@
       <c r="C104" s="8"/>
       <c r="D104" s="7"/>
       <c r="E104" s="7" t="s">
-        <v>134</v>
+        <v>33</v>
       </c>
       <c r="F104" s="7"/>
       <c r="G104" s="7"/>
@@ -3657,13 +3581,13 @@
       <c r="A105" s="7"/>
       <c r="B105" s="7"/>
       <c r="C105" s="8" t="s">
-        <v>122</v>
+        <v>78</v>
       </c>
       <c r="D105" s="7" t="s">
-        <v>42</v>
+        <v>79</v>
       </c>
       <c r="E105" s="7" t="s">
-        <v>56</v>
+        <v>6</v>
       </c>
       <c r="F105" s="7"/>
       <c r="G105" s="7"/>
@@ -3672,31 +3596,31 @@
       <c r="A106" s="7"/>
       <c r="B106" s="7"/>
       <c r="C106" s="8" t="s">
-        <v>123</v>
+        <v>30</v>
       </c>
       <c r="D106" s="7"/>
       <c r="E106" s="10" t="s">
-        <v>136</v>
+        <v>121</v>
       </c>
       <c r="F106" s="7"/>
       <c r="G106" s="10"/>
     </row>
     <row r="107" spans="1:7" ht="40.5">
       <c r="A107" s="4" t="s">
-        <v>30</v>
+        <v>122</v>
       </c>
       <c r="B107" s="4" t="s">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="C107" s="5" t="s">
-        <v>124</v>
+        <v>55</v>
       </c>
       <c r="D107" s="4"/>
       <c r="E107" s="4" t="s">
-        <v>61</v>
+        <v>123</v>
       </c>
       <c r="F107" s="4" t="s">
-        <v>71</v>
+        <v>13</v>
       </c>
       <c r="G107" s="4"/>
     </row>
@@ -3706,10 +3630,10 @@
       <c r="C108" s="8"/>
       <c r="D108" s="7"/>
       <c r="E108" s="7" t="s">
-        <v>60</v>
+        <v>124</v>
       </c>
       <c r="F108" s="7" t="s">
-        <v>16</v>
+        <v>58</v>
       </c>
       <c r="G108" s="7"/>
     </row>
@@ -3719,7 +3643,7 @@
       <c r="C109" s="8"/>
       <c r="D109" s="7"/>
       <c r="E109" s="7" t="s">
-        <v>140</v>
+        <v>125</v>
       </c>
       <c r="F109" s="7"/>
       <c r="G109" s="7"/>
@@ -3730,7 +3654,7 @@
       <c r="C110" s="8"/>
       <c r="D110" s="7"/>
       <c r="E110" s="7" t="s">
-        <v>18</v>
+        <v>60</v>
       </c>
       <c r="F110" s="7"/>
       <c r="G110" s="7"/>
@@ -3741,7 +3665,7 @@
       <c r="C111" s="8"/>
       <c r="D111" s="7"/>
       <c r="E111" s="12" t="s">
-        <v>141</v>
+        <v>126</v>
       </c>
       <c r="F111" s="7"/>
       <c r="G111" s="7"/>
@@ -3750,11 +3674,11 @@
       <c r="A112" s="7"/>
       <c r="B112" s="7"/>
       <c r="C112" s="8" t="s">
-        <v>99</v>
+        <v>63</v>
       </c>
       <c r="D112" s="7"/>
       <c r="E112" s="7" t="s">
-        <v>59</v>
+        <v>9</v>
       </c>
       <c r="F112" s="7"/>
       <c r="G112" s="7"/>
@@ -3765,7 +3689,7 @@
       <c r="C113" s="8"/>
       <c r="D113" s="7"/>
       <c r="E113" s="7" t="s">
-        <v>57</v>
+        <v>7</v>
       </c>
       <c r="F113" s="7"/>
       <c r="G113" s="7"/>
@@ -3776,7 +3700,7 @@
       <c r="C114" s="8"/>
       <c r="D114" s="7"/>
       <c r="E114" s="7" t="s">
-        <v>140</v>
+        <v>125</v>
       </c>
       <c r="F114" s="7"/>
       <c r="G114" s="7"/>
@@ -3787,7 +3711,7 @@
       <c r="C115" s="8"/>
       <c r="D115" s="7"/>
       <c r="E115" s="7" t="s">
-        <v>18</v>
+        <v>60</v>
       </c>
       <c r="F115" s="7"/>
       <c r="G115" s="7"/>
@@ -3796,13 +3720,13 @@
       <c r="A116" s="7"/>
       <c r="B116" s="7"/>
       <c r="C116" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="D116" s="7" t="s">
         <v>117</v>
       </c>
-      <c r="D116" s="7" t="s">
-        <v>137</v>
-      </c>
       <c r="E116" s="7" t="s">
-        <v>54</v>
+        <v>4</v>
       </c>
       <c r="F116" s="7"/>
       <c r="G116" s="7"/>
@@ -3813,7 +3737,7 @@
       <c r="C117" s="8"/>
       <c r="D117" s="7"/>
       <c r="E117" s="12" t="s">
-        <v>135</v>
+        <v>116</v>
       </c>
       <c r="F117" s="7"/>
       <c r="G117" s="7"/>
@@ -3823,10 +3747,10 @@
       <c r="B118" s="7"/>
       <c r="C118" s="8"/>
       <c r="D118" s="7" t="s">
-        <v>138</v>
+        <v>118</v>
       </c>
       <c r="E118" s="7" t="s">
-        <v>142</v>
+        <v>119</v>
       </c>
       <c r="F118" s="7"/>
       <c r="G118" s="7"/>
@@ -3836,10 +3760,10 @@
       <c r="B119" s="7"/>
       <c r="C119" s="8"/>
       <c r="D119" s="7" t="s">
-        <v>139</v>
+        <v>120</v>
       </c>
       <c r="E119" s="7" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="F119" s="7"/>
       <c r="G119" s="7"/>
@@ -3850,7 +3774,7 @@
       <c r="C120" s="8"/>
       <c r="D120" s="7"/>
       <c r="E120" s="7" t="s">
-        <v>134</v>
+        <v>33</v>
       </c>
       <c r="F120" s="7"/>
       <c r="G120" s="7"/>
@@ -3859,13 +3783,13 @@
       <c r="A121" s="7"/>
       <c r="B121" s="7"/>
       <c r="C121" s="8" t="s">
-        <v>122</v>
+        <v>78</v>
       </c>
       <c r="D121" s="7" t="s">
-        <v>42</v>
+        <v>79</v>
       </c>
       <c r="E121" s="7" t="s">
-        <v>56</v>
+        <v>6</v>
       </c>
       <c r="F121" s="7"/>
       <c r="G121" s="7"/>
@@ -3874,27 +3798,27 @@
       <c r="A122" s="7"/>
       <c r="B122" s="7"/>
       <c r="C122" s="8" t="s">
-        <v>123</v>
+        <v>30</v>
       </c>
       <c r="D122" s="7"/>
       <c r="E122" s="10" t="s">
-        <v>136</v>
+        <v>121</v>
       </c>
       <c r="F122" s="7"/>
       <c r="G122" s="10"/>
     </row>
     <row r="123" spans="1:7" ht="40.5">
       <c r="A123" s="4" t="s">
-        <v>31</v>
+        <v>127</v>
       </c>
       <c r="B123" s="4" t="s">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="C123" s="5"/>
       <c r="D123" s="4"/>
       <c r="E123" s="4"/>
       <c r="F123" s="4" t="s">
-        <v>71</v>
+        <v>13</v>
       </c>
       <c r="G123" s="4"/>
     </row>
@@ -3902,12 +3826,12 @@
       <c r="A124" s="7"/>
       <c r="B124" s="7"/>
       <c r="C124" s="7" t="s">
-        <v>150</v>
+        <v>38</v>
       </c>
       <c r="D124" s="7"/>
       <c r="E124" s="7"/>
       <c r="F124" s="7" t="s">
-        <v>16</v>
+        <v>58</v>
       </c>
       <c r="G124" s="7"/>
     </row>
@@ -3922,18 +3846,18 @@
     </row>
     <row r="126" spans="1:7" ht="40.5">
       <c r="A126" s="4" t="s">
-        <v>4</v>
+        <v>128</v>
       </c>
       <c r="B126" s="4" t="s">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="C126" s="5"/>
       <c r="D126" s="4"/>
       <c r="E126" s="4" t="s">
-        <v>148</v>
+        <v>36</v>
       </c>
       <c r="F126" s="4" t="s">
-        <v>71</v>
+        <v>13</v>
       </c>
       <c r="G126" s="4"/>
     </row>
@@ -3941,14 +3865,14 @@
       <c r="A127" s="7"/>
       <c r="B127" s="7"/>
       <c r="C127" s="7" t="s">
-        <v>151</v>
+        <v>129</v>
       </c>
       <c r="D127" s="7"/>
       <c r="E127" s="7" t="s">
-        <v>149</v>
+        <v>37</v>
       </c>
       <c r="F127" s="7" t="s">
-        <v>16</v>
+        <v>58</v>
       </c>
       <c r="G127" s="7"/>
     </row>
@@ -3963,13 +3887,13 @@
     </row>
     <row r="129" spans="1:7" ht="67.5">
       <c r="A129" s="4" t="s">
-        <v>32</v>
+        <v>130</v>
       </c>
       <c r="B129" s="4" t="s">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="C129" s="14" t="s">
-        <v>152</v>
+        <v>39</v>
       </c>
       <c r="D129" s="4"/>
       <c r="E129" s="4"/>
@@ -3996,25 +3920,25 @@
     </row>
     <row r="132" spans="1:7" ht="54">
       <c r="A132" s="4" t="s">
-        <v>144</v>
+        <v>34</v>
       </c>
       <c r="B132" s="4" t="s">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="C132" s="5" t="s">
-        <v>66</v>
+        <v>131</v>
       </c>
       <c r="D132" s="4" t="s">
-        <v>143</v>
+        <v>132</v>
       </c>
       <c r="E132" s="4" t="s">
-        <v>145</v>
+        <v>133</v>
       </c>
       <c r="F132" s="4" t="s">
-        <v>33</v>
+        <v>134</v>
       </c>
       <c r="G132" s="4" t="s">
-        <v>34</v>
+        <v>135</v>
       </c>
     </row>
     <row r="133" spans="1:7">
@@ -4023,7 +3947,7 @@
       <c r="C133" s="8"/>
       <c r="D133" s="7"/>
       <c r="E133" s="7" t="s">
-        <v>146</v>
+        <v>136</v>
       </c>
       <c r="F133" s="7"/>
       <c r="G133" s="7"/>
@@ -4034,7 +3958,7 @@
       <c r="C134" s="8"/>
       <c r="D134" s="7"/>
       <c r="E134" s="7" t="s">
-        <v>147</v>
+        <v>35</v>
       </c>
       <c r="F134" s="7"/>
       <c r="G134" s="7"/>
@@ -4045,7 +3969,7 @@
       <c r="C135" s="8"/>
       <c r="D135" s="7"/>
       <c r="E135" s="7" t="s">
-        <v>153</v>
+        <v>40</v>
       </c>
       <c r="F135" s="7"/>
       <c r="G135" s="7"/>
@@ -4054,16 +3978,16 @@
       <c r="A136" s="7"/>
       <c r="B136" s="7"/>
       <c r="C136" s="8" t="s">
-        <v>67</v>
+        <v>137</v>
       </c>
       <c r="D136" s="7" t="s">
-        <v>68</v>
+        <v>91</v>
       </c>
       <c r="E136" s="7" t="s">
-        <v>147</v>
+        <v>35</v>
       </c>
       <c r="F136" s="7" t="s">
-        <v>35</v>
+        <v>138</v>
       </c>
       <c r="G136" s="7"/>
     </row>
@@ -4073,17 +3997,17 @@
       <c r="C137" s="8"/>
       <c r="D137" s="7"/>
       <c r="E137" s="7" t="s">
-        <v>153</v>
+        <v>40</v>
       </c>
       <c r="F137" s="7"/>
       <c r="G137" s="7"/>
     </row>
     <row r="138" spans="1:7" ht="40.5">
       <c r="A138" s="4" t="s">
-        <v>62</v>
+        <v>10</v>
       </c>
       <c r="B138" s="4" t="s">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="C138" s="5"/>
       <c r="D138" s="4"/>
@@ -4095,241 +4019,197 @@
       <c r="A139" s="7"/>
       <c r="B139" s="7"/>
       <c r="C139" s="7" t="s">
-        <v>154</v>
+        <v>139</v>
       </c>
       <c r="D139" s="7"/>
       <c r="E139" s="7"/>
       <c r="F139" s="7"/>
       <c r="G139" s="7"/>
     </row>
-    <row r="140" spans="1:7" ht="27">
+    <row r="140" spans="1:7" ht="40.5">
       <c r="A140" s="7"/>
       <c r="B140" s="7"/>
       <c r="C140" s="7" t="s">
-        <v>158</v>
+        <v>140</v>
       </c>
       <c r="D140" s="7"/>
       <c r="E140" s="7"/>
       <c r="F140" s="7"/>
       <c r="G140" s="7"/>
     </row>
-    <row r="141" spans="1:7" ht="27">
+    <row r="141" spans="1:7" ht="40.5">
       <c r="A141" s="7"/>
       <c r="B141" s="7"/>
       <c r="C141" s="7" t="s">
-        <v>155</v>
+        <v>42</v>
       </c>
       <c r="D141" s="7"/>
       <c r="E141" s="7"/>
       <c r="F141" s="7"/>
       <c r="G141" s="7"/>
     </row>
-    <row r="142" spans="1:7" ht="27">
+    <row r="142" spans="1:7" ht="40.5">
       <c r="A142" s="7"/>
       <c r="B142" s="7"/>
       <c r="C142" s="7" t="s">
-        <v>156</v>
+        <v>43</v>
       </c>
       <c r="D142" s="7"/>
       <c r="E142" s="7"/>
       <c r="F142" s="7"/>
       <c r="G142" s="7"/>
     </row>
-    <row r="143" spans="1:7" ht="27">
-      <c r="A143" s="7"/>
-      <c r="B143" s="7"/>
-      <c r="C143" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="D143" s="7"/>
-      <c r="E143" s="7"/>
-      <c r="F143" s="7"/>
-      <c r="G143" s="7"/>
-    </row>
-    <row r="144" spans="1:7" ht="27">
+    <row r="143" spans="1:7" ht="40.5">
+      <c r="A143" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="B143" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="C143" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="D143" s="4"/>
+      <c r="E143" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="F143" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G143" s="4"/>
+    </row>
+    <row r="144" spans="1:7">
       <c r="A144" s="7"/>
       <c r="B144" s="7"/>
-      <c r="C144" s="7" t="s">
-        <v>157</v>
-      </c>
+      <c r="C144" s="8"/>
       <c r="D144" s="7"/>
-      <c r="E144" s="7"/>
-      <c r="F144" s="7"/>
+      <c r="E144" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="F144" s="7" t="s">
+        <v>58</v>
+      </c>
       <c r="G144" s="7"/>
     </row>
-    <row r="145" spans="1:7" ht="27">
+    <row r="145" spans="1:7">
       <c r="A145" s="7"/>
       <c r="B145" s="7"/>
-      <c r="C145" s="7" t="s">
-        <v>160</v>
+      <c r="C145" s="8" t="s">
+        <v>63</v>
       </c>
       <c r="D145" s="7"/>
-      <c r="E145" s="7"/>
+      <c r="E145" s="7" t="s">
+        <v>9</v>
+      </c>
       <c r="F145" s="7"/>
       <c r="G145" s="7"/>
     </row>
-    <row r="146" spans="1:7" ht="40.5">
+    <row r="146" spans="1:7">
       <c r="A146" s="7"/>
       <c r="B146" s="7"/>
-      <c r="C146" s="7" t="s">
-        <v>161</v>
-      </c>
+      <c r="C146" s="8"/>
       <c r="D146" s="7"/>
-      <c r="E146" s="7"/>
+      <c r="E146" s="7" t="s">
+        <v>7</v>
+      </c>
       <c r="F146" s="7"/>
       <c r="G146" s="7"/>
     </row>
-    <row r="147" spans="1:7" ht="40.5">
-      <c r="A147" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="B147" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="C147" s="5" t="s">
-        <v>115</v>
-      </c>
-      <c r="D147" s="4"/>
-      <c r="E147" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="F147" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="G147" s="4"/>
-    </row>
-    <row r="148" spans="1:7">
+    <row r="147" spans="1:7" ht="67.5">
+      <c r="A147" s="7"/>
+      <c r="B147" s="7"/>
+      <c r="C147" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="D147" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="E147" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="F147" s="7"/>
+      <c r="G147" s="7"/>
+    </row>
+    <row r="148" spans="1:7" ht="67.5">
       <c r="A148" s="7"/>
       <c r="B148" s="7"/>
       <c r="C148" s="8"/>
-      <c r="D148" s="7"/>
+      <c r="D148" s="7" t="s">
+        <v>118</v>
+      </c>
       <c r="E148" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="F148" s="7" t="s">
-        <v>16</v>
-      </c>
+        <v>33</v>
+      </c>
+      <c r="F148" s="7"/>
       <c r="G148" s="7"/>
     </row>
-    <row r="149" spans="1:7">
+    <row r="149" spans="1:7" ht="27">
       <c r="A149" s="7"/>
       <c r="B149" s="7"/>
       <c r="C149" s="8" t="s">
-        <v>99</v>
-      </c>
-      <c r="D149" s="7"/>
+        <v>78</v>
+      </c>
+      <c r="D149" s="7" t="s">
+        <v>79</v>
+      </c>
       <c r="E149" s="7" t="s">
-        <v>59</v>
+        <v>6</v>
       </c>
       <c r="F149" s="7"/>
       <c r="G149" s="7"/>
     </row>
-    <row r="150" spans="1:7">
+    <row r="150" spans="1:7" ht="40.5">
       <c r="A150" s="7"/>
       <c r="B150" s="7"/>
-      <c r="C150" s="8"/>
+      <c r="C150" s="8" t="s">
+        <v>30</v>
+      </c>
       <c r="D150" s="7"/>
-      <c r="E150" s="7" t="s">
-        <v>57</v>
+      <c r="E150" s="10" t="s">
+        <v>121</v>
       </c>
       <c r="F150" s="7"/>
-      <c r="G150" s="7"/>
-    </row>
-    <row r="151" spans="1:7" ht="67.5">
-      <c r="A151" s="7"/>
-      <c r="B151" s="7"/>
-      <c r="C151" s="8" t="s">
-        <v>117</v>
-      </c>
-      <c r="D151" s="7" t="s">
-        <v>137</v>
-      </c>
-      <c r="E151" s="7" t="s">
+      <c r="G150" s="10"/>
+    </row>
+    <row r="151" spans="1:7" ht="40.5">
+      <c r="A151" s="4" t="s">
         <v>142</v>
       </c>
-      <c r="F151" s="7"/>
-      <c r="G151" s="7"/>
-    </row>
-    <row r="152" spans="1:7" ht="67.5">
+      <c r="B151" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="C151" s="5"/>
+      <c r="D151" s="4"/>
+      <c r="E151" s="4"/>
+      <c r="F151" s="4"/>
+      <c r="G151" s="4"/>
+    </row>
+    <row r="152" spans="1:7">
       <c r="A152" s="7"/>
       <c r="B152" s="7"/>
       <c r="C152" s="8"/>
-      <c r="D152" s="7" t="s">
-        <v>138</v>
-      </c>
-      <c r="E152" s="7" t="s">
-        <v>134</v>
-      </c>
+      <c r="D152" s="7"/>
+      <c r="E152" s="7"/>
       <c r="F152" s="7"/>
       <c r="G152" s="7"/>
     </row>
-    <row r="153" spans="1:7" ht="27">
+    <row r="153" spans="1:7">
       <c r="A153" s="7"/>
       <c r="B153" s="7"/>
-      <c r="C153" s="8" t="s">
-        <v>122</v>
-      </c>
-      <c r="D153" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="E153" s="7" t="s">
-        <v>56</v>
-      </c>
+      <c r="C153" s="8"/>
+      <c r="D153" s="7"/>
+      <c r="E153" s="7"/>
       <c r="F153" s="7"/>
       <c r="G153" s="7"/>
     </row>
-    <row r="154" spans="1:7" ht="40.5">
-      <c r="A154" s="7"/>
-      <c r="B154" s="7"/>
-      <c r="C154" s="8" t="s">
-        <v>123</v>
-      </c>
-      <c r="D154" s="7"/>
-      <c r="E154" s="10" t="s">
-        <v>136</v>
-      </c>
-      <c r="F154" s="7"/>
-      <c r="G154" s="10"/>
-    </row>
-    <row r="155" spans="1:7" ht="40.5">
-      <c r="A155" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="B155" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="C155" s="5"/>
-      <c r="D155" s="4"/>
-      <c r="E155" s="4"/>
-      <c r="F155" s="4"/>
-      <c r="G155" s="4"/>
-    </row>
-    <row r="156" spans="1:7">
-      <c r="A156" s="7"/>
-      <c r="B156" s="7"/>
-      <c r="C156" s="8"/>
-      <c r="D156" s="7"/>
-      <c r="E156" s="7"/>
-      <c r="F156" s="7"/>
-      <c r="G156" s="7"/>
-    </row>
-    <row r="157" spans="1:7">
-      <c r="A157" s="7"/>
-      <c r="B157" s="7"/>
-      <c r="C157" s="8"/>
-      <c r="D157" s="7"/>
-      <c r="E157" s="7"/>
-      <c r="F157" s="7"/>
-      <c r="G157" s="7"/>
-    </row>
-    <row r="158" spans="1:7">
-      <c r="D158" s="9"/>
-      <c r="E158" s="9"/>
-      <c r="F158" s="9"/>
-      <c r="G158" s="9"/>
+    <row r="154" spans="1:7">
+      <c r="D154" s="9"/>
+      <c r="E154" s="9"/>
+      <c r="F154" s="9"/>
+      <c r="G154" s="9"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G145"/>
+  <autoFilter ref="A1:G142"/>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -4347,112 +4227,112 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="7" t="s">
-        <v>57</v>
+        <v>7</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" s="7" t="s">
-        <v>58</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="7" t="s">
-        <v>18</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="7" t="s">
-        <v>19</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" s="7" t="s">
-        <v>59</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" s="7" t="s">
-        <v>57</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" s="7" t="s">
-        <v>58</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" s="7" t="s">
-        <v>18</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" s="7" t="s">
-        <v>19</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" s="7" t="s">
-        <v>59</v>
+        <v>9</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" s="7" t="s">
-        <v>57</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12" spans="1:1">
       <c r="A12" s="7" t="s">
-        <v>58</v>
+        <v>8</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" s="7" t="s">
-        <v>18</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:1">
       <c r="A14" s="7" t="s">
-        <v>19</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" s="7" t="s">
-        <v>58</v>
+        <v>8</v>
       </c>
     </row>
     <row r="16" spans="1:1">
       <c r="A16" s="7" t="s">
-        <v>18</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" s="7" t="s">
-        <v>19</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18" spans="1:1">
       <c r="A18" s="7" t="s">
-        <v>58</v>
+        <v>8</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" s="7" t="s">
-        <v>18</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" s="7" t="s">
-        <v>19</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" s="7" t="s">
-        <v>58</v>
+        <v>8</v>
       </c>
     </row>
     <row r="22" spans="1:1">
       <c r="A22" s="7" t="s">
-        <v>59</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>

--- a/internal_doc/05.测试设计/可靠性测试/主子表故障测试_review.xlsx
+++ b/internal_doc/05.测试设计/可靠性测试/主子表故障测试_review.xlsx
@@ -12,7 +12,7 @@
     <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$G$142</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$G$143</definedName>
   </definedNames>
   <calcPr calcId="124519"/>
 </workbook>
@@ -973,7 +973,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A143" authorId="0">
+    <comment ref="A144" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1038,7 +1038,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C147" authorId="0">
+    <comment ref="C148" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1069,7 +1069,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="347" uniqueCount="143">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="352" uniqueCount="145">
   <si>
     <t>dataRG连续降备</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1223,10 +1223,6 @@
   </si>
   <si>
     <t>断网后组内重新选主；恢复网络后查看是否从新的主节点同步数据，数据完整且跟新主数据一致；子表挂载成功在对应主表做基本操作成功(如insert数据)；</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>dataRG主节点与dataRG备节点网络单通</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -1677,6 +1673,18 @@
   </si>
   <si>
     <t>磁盘损坏（低优先级）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>故障时间最小时间7s则不触发选主，attachCL成功；故障超过7s后组内重新选主，恢复网络后在新主attachCL成功；</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>dataRG主节点与dataRG备节点网络单通</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>dataRG备节点与其他备节点网络单通</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2162,7 +2170,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G154"/>
+  <dimension ref="A1:G155"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="9.875" style="6" customWidth="1"/>
@@ -2177,40 +2185,40 @@
   <sheetData>
     <row r="1" spans="1:7" s="3" customFormat="1" ht="27">
       <c r="A1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="C1" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="D1" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="E1" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="F1" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="G1" s="2" t="s">
         <v>51</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>52</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="40.5">
       <c r="A2" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="B2" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="C2" s="5" t="s">
         <v>54</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>55</v>
       </c>
       <c r="D2" s="4"/>
       <c r="E2" s="4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F2" s="4" t="s">
         <v>11</v>
@@ -2223,10 +2231,10 @@
       <c r="C3" s="8"/>
       <c r="D3" s="7"/>
       <c r="E3" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="F3" s="7" t="s">
         <v>57</v>
-      </c>
-      <c r="F3" s="7" t="s">
-        <v>58</v>
       </c>
       <c r="G3" s="7"/>
     </row>
@@ -2236,7 +2244,7 @@
       <c r="C4" s="8"/>
       <c r="D4" s="7"/>
       <c r="E4" s="7" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F4" s="7" t="s">
         <v>41</v>
@@ -2249,10 +2257,10 @@
       <c r="C5" s="8"/>
       <c r="D5" s="7"/>
       <c r="E5" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="F5" s="7" t="s">
         <v>60</v>
-      </c>
-      <c r="F5" s="7" t="s">
-        <v>61</v>
       </c>
       <c r="G5" s="7"/>
     </row>
@@ -2262,10 +2270,10 @@
       <c r="C6" s="8"/>
       <c r="D6" s="7"/>
       <c r="E6" s="7" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G6" s="7"/>
     </row>
@@ -2273,11 +2281,11 @@
       <c r="A7" s="7"/>
       <c r="B7" s="7"/>
       <c r="C7" s="8" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D7" s="7"/>
       <c r="E7" s="7" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F7" s="7" t="s">
         <v>14</v>
@@ -2290,10 +2298,10 @@
       <c r="C8" s="8"/>
       <c r="D8" s="7"/>
       <c r="E8" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="F8" s="7" t="s">
         <v>57</v>
-      </c>
-      <c r="F8" s="7" t="s">
-        <v>58</v>
       </c>
       <c r="G8" s="7"/>
     </row>
@@ -2303,7 +2311,7 @@
       <c r="C9" s="8"/>
       <c r="D9" s="7"/>
       <c r="E9" s="7" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F9" s="7" t="s">
         <v>14</v>
@@ -2316,7 +2324,7 @@
       <c r="C10" s="8"/>
       <c r="D10" s="7"/>
       <c r="E10" s="7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F10" s="7" t="s">
         <v>12</v>
@@ -2329,10 +2337,10 @@
       <c r="C11" s="8"/>
       <c r="D11" s="7"/>
       <c r="E11" s="7" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F11" s="7" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G11" s="7"/>
     </row>
@@ -2340,16 +2348,16 @@
       <c r="A12" s="7"/>
       <c r="B12" s="7"/>
       <c r="C12" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="D12" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="D12" s="7" t="s">
+      <c r="E12" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="F12" s="7" t="s">
         <v>65</v>
-      </c>
-      <c r="E12" s="7" t="s">
-        <v>56</v>
-      </c>
-      <c r="F12" s="7" t="s">
-        <v>66</v>
       </c>
       <c r="G12" s="7"/>
     </row>
@@ -2359,7 +2367,7 @@
       <c r="C13" s="8"/>
       <c r="D13" s="7"/>
       <c r="E13" s="11" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F13" s="7"/>
       <c r="G13" s="7"/>
@@ -2369,13 +2377,13 @@
       <c r="B14" s="7"/>
       <c r="C14" s="8"/>
       <c r="D14" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="E14" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="F14" s="7" t="s">
         <v>67</v>
-      </c>
-      <c r="E14" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="F14" s="7" t="s">
-        <v>68</v>
       </c>
       <c r="G14" s="7"/>
     </row>
@@ -2384,13 +2392,13 @@
       <c r="B15" s="7"/>
       <c r="C15" s="8"/>
       <c r="D15" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="E15" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="F15" s="7" t="s">
         <v>69</v>
-      </c>
-      <c r="E15" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="F15" s="7" t="s">
-        <v>70</v>
       </c>
       <c r="G15" s="7"/>
     </row>
@@ -2400,10 +2408,10 @@
       <c r="C16" s="8"/>
       <c r="D16" s="7"/>
       <c r="E16" s="7" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F16" s="7" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G16" s="7"/>
     </row>
@@ -2411,16 +2419,16 @@
       <c r="A17" s="7"/>
       <c r="B17" s="7"/>
       <c r="C17" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="D17" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="D17" s="7" t="s">
+      <c r="E17" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="F17" s="7" t="s">
         <v>72</v>
-      </c>
-      <c r="E17" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="F17" s="7" t="s">
-        <v>73</v>
       </c>
       <c r="G17" s="7"/>
     </row>
@@ -2430,10 +2438,10 @@
       <c r="C18" s="8"/>
       <c r="D18" s="7"/>
       <c r="E18" s="7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F18" s="7" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G18" s="7"/>
     </row>
@@ -2443,10 +2451,10 @@
       <c r="C19" s="8"/>
       <c r="D19" s="7"/>
       <c r="E19" s="7" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F19" s="7" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G19" s="7"/>
     </row>
@@ -2454,16 +2462,16 @@
       <c r="A20" s="7"/>
       <c r="B20" s="7"/>
       <c r="C20" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="D20" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="D20" s="7" t="s">
+      <c r="E20" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="F20" s="7" t="s">
         <v>76</v>
-      </c>
-      <c r="E20" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="F20" s="7" t="s">
-        <v>77</v>
       </c>
       <c r="G20" s="7"/>
     </row>
@@ -2473,10 +2481,10 @@
       <c r="C21" s="8"/>
       <c r="D21" s="7"/>
       <c r="E21" s="7" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F21" s="7" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G21" s="7"/>
     </row>
@@ -2484,13 +2492,13 @@
       <c r="A22" s="7"/>
       <c r="B22" s="7"/>
       <c r="C22" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="D22" s="7" t="s">
         <v>78</v>
       </c>
-      <c r="D22" s="7" t="s">
-        <v>79</v>
-      </c>
       <c r="E22" s="7" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F22" s="7" t="s">
         <v>15</v>
@@ -2505,32 +2513,32 @@
       </c>
       <c r="D23" s="7"/>
       <c r="E23" s="7" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F23" s="7" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G23" s="7"/>
     </row>
     <row r="24" spans="1:7" ht="54">
       <c r="A24" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B24" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="C24" s="5" t="s">
         <v>54</v>
-      </c>
-      <c r="C24" s="5" t="s">
-        <v>55</v>
       </c>
       <c r="D24" s="4"/>
       <c r="E24" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="F24" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="G24" s="4" t="s">
         <v>81</v>
-      </c>
-      <c r="F24" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="G24" s="4" t="s">
-        <v>82</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -2542,7 +2550,7 @@
         <v>18</v>
       </c>
       <c r="F25" s="7" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G25" s="7"/>
     </row>
@@ -2552,7 +2560,7 @@
       <c r="C26" s="8"/>
       <c r="D26" s="7"/>
       <c r="E26" s="7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F26" s="7"/>
       <c r="G26" s="7"/>
@@ -2574,7 +2582,7 @@
       <c r="C28" s="8"/>
       <c r="D28" s="7"/>
       <c r="E28" s="7" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F28" s="7"/>
       <c r="G28" s="7"/>
@@ -2583,7 +2591,7 @@
       <c r="A29" s="7"/>
       <c r="B29" s="7"/>
       <c r="C29" s="8" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D29" s="7"/>
       <c r="E29" s="7" t="s">
@@ -2609,7 +2617,7 @@
       <c r="C31" s="8"/>
       <c r="D31" s="7"/>
       <c r="E31" s="7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F31" s="7"/>
       <c r="G31" s="7"/>
@@ -2631,7 +2639,7 @@
       <c r="C33" s="8"/>
       <c r="D33" s="7"/>
       <c r="E33" s="7" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F33" s="7"/>
       <c r="G33" s="7"/>
@@ -2640,10 +2648,10 @@
       <c r="A34" s="7"/>
       <c r="B34" s="7"/>
       <c r="C34" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="D34" s="7" t="s">
         <v>64</v>
-      </c>
-      <c r="D34" s="7" t="s">
-        <v>65</v>
       </c>
       <c r="E34" s="7" t="s">
         <v>17</v>
@@ -2667,10 +2675,10 @@
       <c r="B36" s="7"/>
       <c r="C36" s="8"/>
       <c r="D36" s="7" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E36" s="12" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F36" s="7"/>
       <c r="G36" s="7"/>
@@ -2680,7 +2688,7 @@
       <c r="B37" s="7"/>
       <c r="C37" s="8"/>
       <c r="D37" s="7" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E37" s="7" t="s">
         <v>16</v>
@@ -2692,10 +2700,10 @@
       <c r="A38" s="7"/>
       <c r="B38" s="7"/>
       <c r="C38" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="D38" s="7" t="s">
         <v>71</v>
-      </c>
-      <c r="D38" s="7" t="s">
-        <v>72</v>
       </c>
       <c r="E38" s="7" t="s">
         <v>18</v>
@@ -2718,10 +2726,10 @@
       <c r="A40" s="7"/>
       <c r="B40" s="7"/>
       <c r="C40" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="D40" s="7" t="s">
         <v>75</v>
-      </c>
-      <c r="D40" s="7" t="s">
-        <v>76</v>
       </c>
       <c r="E40" s="7" t="s">
         <v>18</v>
@@ -2744,10 +2752,10 @@
       <c r="A42" s="7"/>
       <c r="B42" s="7"/>
       <c r="C42" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="D42" s="7" t="s">
         <v>78</v>
-      </c>
-      <c r="D42" s="7" t="s">
-        <v>79</v>
       </c>
       <c r="E42" s="7" t="s">
         <v>18</v>
@@ -2770,23 +2778,23 @@
     </row>
     <row r="44" spans="1:7" ht="40.5">
       <c r="A44" s="4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B44" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="C44" s="5" t="s">
         <v>54</v>
-      </c>
-      <c r="C44" s="5" t="s">
-        <v>55</v>
       </c>
       <c r="D44" s="4"/>
       <c r="E44" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="F44" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="G44" s="4" t="s">
         <v>84</v>
-      </c>
-      <c r="F44" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="G44" s="4" t="s">
-        <v>85</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -2798,7 +2806,7 @@
         <v>21</v>
       </c>
       <c r="F45" s="7" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G45" s="7"/>
     </row>
@@ -2819,7 +2827,7 @@
       <c r="C47" s="8"/>
       <c r="D47" s="7"/>
       <c r="E47" s="7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F47" s="7"/>
       <c r="G47" s="7"/>
@@ -2839,11 +2847,11 @@
       <c r="A49" s="7"/>
       <c r="B49" s="7"/>
       <c r="C49" s="8" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D49" s="7"/>
       <c r="E49" s="7" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F49" s="7"/>
       <c r="G49" s="7"/>
@@ -2876,7 +2884,7 @@
       <c r="C52" s="8"/>
       <c r="D52" s="7"/>
       <c r="E52" s="7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F52" s="7"/>
       <c r="G52" s="7"/>
@@ -2885,10 +2893,10 @@
       <c r="A53" s="7"/>
       <c r="B53" s="7"/>
       <c r="C53" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="D53" s="7" t="s">
         <v>64</v>
-      </c>
-      <c r="D53" s="7" t="s">
-        <v>65</v>
       </c>
       <c r="E53" s="7" t="s">
         <v>19</v>
@@ -2901,7 +2909,7 @@
       <c r="B54" s="7"/>
       <c r="C54" s="8"/>
       <c r="D54" s="7" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E54" s="7" t="s">
         <v>22</v>
@@ -2914,10 +2922,10 @@
       <c r="B55" s="7"/>
       <c r="C55" s="8"/>
       <c r="D55" s="7" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E55" s="7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F55" s="7"/>
       <c r="G55" s="7"/>
@@ -2937,10 +2945,10 @@
       <c r="A57" s="7"/>
       <c r="B57" s="7"/>
       <c r="C57" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="D57" s="7" t="s">
         <v>71</v>
-      </c>
-      <c r="D57" s="7" t="s">
-        <v>72</v>
       </c>
       <c r="E57" s="7" t="s">
         <v>22</v>
@@ -2954,7 +2962,7 @@
       <c r="C58" s="8"/>
       <c r="D58" s="7"/>
       <c r="E58" s="12" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F58" s="7"/>
       <c r="G58" s="7"/>
@@ -2974,10 +2982,10 @@
       <c r="A60" s="7"/>
       <c r="B60" s="7"/>
       <c r="C60" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="D60" s="7" t="s">
         <v>75</v>
-      </c>
-      <c r="D60" s="7" t="s">
-        <v>76</v>
       </c>
       <c r="E60" s="7" t="s">
         <v>22</v>
@@ -3000,10 +3008,10 @@
       <c r="A62" s="7"/>
       <c r="B62" s="7"/>
       <c r="C62" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="D62" s="7" t="s">
         <v>78</v>
-      </c>
-      <c r="D62" s="7" t="s">
-        <v>79</v>
       </c>
       <c r="E62" s="7" t="s">
         <v>22</v>
@@ -3035,20 +3043,20 @@
     </row>
     <row r="65" spans="1:7" ht="27">
       <c r="A65" s="4" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B65" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="C65" s="5" t="s">
         <v>54</v>
-      </c>
-      <c r="C65" s="5" t="s">
-        <v>55</v>
       </c>
       <c r="D65" s="4"/>
       <c r="E65" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="F65" s="4" t="s">
         <v>87</v>
-      </c>
-      <c r="F65" s="4" t="s">
-        <v>88</v>
       </c>
       <c r="G65" s="4"/>
     </row>
@@ -3058,10 +3066,10 @@
       <c r="C66" s="8"/>
       <c r="D66" s="7"/>
       <c r="E66" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="F66" s="7" t="s">
         <v>89</v>
-      </c>
-      <c r="F66" s="7" t="s">
-        <v>90</v>
       </c>
       <c r="G66" s="7"/>
     </row>
@@ -3080,7 +3088,7 @@
       <c r="A68" s="7"/>
       <c r="B68" s="7"/>
       <c r="C68" s="8" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D68" s="7"/>
       <c r="E68" s="7" t="s">
@@ -3093,10 +3101,10 @@
       <c r="A69" s="7"/>
       <c r="B69" s="7"/>
       <c r="C69" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="D69" s="7" t="s">
         <v>91</v>
-      </c>
-      <c r="D69" s="7" t="s">
-        <v>92</v>
       </c>
       <c r="E69" s="7" t="s">
         <v>2</v>
@@ -3117,20 +3125,20 @@
     </row>
     <row r="71" spans="1:7" ht="27">
       <c r="A71" s="4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B71" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="C71" s="5" t="s">
         <v>54</v>
-      </c>
-      <c r="C71" s="5" t="s">
-        <v>55</v>
       </c>
       <c r="D71" s="4"/>
       <c r="E71" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F71" s="4" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G71" s="4"/>
     </row>
@@ -3140,10 +3148,10 @@
       <c r="C72" s="8"/>
       <c r="D72" s="7"/>
       <c r="E72" s="7" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F72" s="7" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="G72" s="7"/>
     </row>
@@ -3153,7 +3161,7 @@
       <c r="C73" s="8"/>
       <c r="D73" s="7"/>
       <c r="E73" s="7" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F73" s="7"/>
       <c r="G73" s="7"/>
@@ -3162,11 +3170,11 @@
       <c r="A74" s="7"/>
       <c r="B74" s="7"/>
       <c r="C74" s="8" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D74" s="7"/>
       <c r="E74" s="7" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F74" s="7"/>
       <c r="G74" s="7"/>
@@ -3175,13 +3183,13 @@
       <c r="A75" s="7"/>
       <c r="B75" s="7"/>
       <c r="C75" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="D75" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="D75" s="7" t="s">
-        <v>92</v>
-      </c>
       <c r="E75" s="7" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F75" s="7"/>
       <c r="G75" s="7"/>
@@ -3192,27 +3200,27 @@
       <c r="C76" s="8"/>
       <c r="D76" s="7"/>
       <c r="E76" s="7" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F76" s="7"/>
       <c r="G76" s="7"/>
     </row>
     <row r="77" spans="1:7" ht="40.5">
       <c r="A77" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B77" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="C77" s="5" t="s">
         <v>54</v>
-      </c>
-      <c r="C77" s="5" t="s">
-        <v>55</v>
       </c>
       <c r="D77" s="4"/>
       <c r="E77" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="F77" s="4" t="s">
         <v>99</v>
-      </c>
-      <c r="F77" s="4" t="s">
-        <v>100</v>
       </c>
       <c r="G77" s="4" t="s">
         <v>25</v>
@@ -3222,14 +3230,14 @@
       <c r="A78" s="7"/>
       <c r="B78" s="7"/>
       <c r="C78" s="8" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D78" s="7"/>
       <c r="E78" s="7" t="s">
         <v>24</v>
       </c>
       <c r="F78" s="7" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="G78" s="7"/>
     </row>
@@ -3237,13 +3245,13 @@
       <c r="A79" s="7"/>
       <c r="B79" s="7"/>
       <c r="C79" s="8" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D79" s="7" t="s">
         <v>23</v>
       </c>
       <c r="E79" s="7" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F79" s="7" t="s">
         <v>27</v>
@@ -3265,13 +3273,13 @@
     </row>
     <row r="81" spans="1:7" ht="27">
       <c r="A81" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="B81" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="C81" s="4" t="s">
         <v>103</v>
-      </c>
-      <c r="B81" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="C81" s="4" t="s">
-        <v>104</v>
       </c>
       <c r="D81" s="4"/>
       <c r="E81" s="4"/>
@@ -3279,7 +3287,7 @@
         <v>28</v>
       </c>
       <c r="G81" s="4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="82" spans="1:7" ht="27">
@@ -3299,12 +3307,12 @@
       <c r="A83" s="7"/>
       <c r="B83" s="7"/>
       <c r="C83" s="7" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D83" s="7"/>
       <c r="E83" s="7"/>
       <c r="F83" s="7" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="G83" s="7"/>
     </row>
@@ -3312,7 +3320,7 @@
       <c r="A84" s="7"/>
       <c r="B84" s="7"/>
       <c r="C84" s="7" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D84" s="7"/>
       <c r="E84" s="7"/>
@@ -3323,20 +3331,20 @@
     </row>
     <row r="85" spans="1:7" ht="27">
       <c r="A85" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B85" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="C85" s="5" t="s">
         <v>54</v>
-      </c>
-      <c r="C85" s="5" t="s">
-        <v>55</v>
       </c>
       <c r="D85" s="4"/>
       <c r="E85" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="F85" s="4" t="s">
         <v>110</v>
-      </c>
-      <c r="F85" s="4" t="s">
-        <v>111</v>
       </c>
       <c r="G85" s="4"/>
     </row>
@@ -3346,10 +3354,10 @@
       <c r="C86" s="8"/>
       <c r="D86" s="7"/>
       <c r="E86" s="7" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F86" s="7" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G86" s="7"/>
     </row>
@@ -3357,11 +3365,11 @@
       <c r="A87" s="7"/>
       <c r="B87" s="7"/>
       <c r="C87" s="8" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D87" s="7"/>
       <c r="E87" s="7" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F87" s="7"/>
       <c r="G87" s="7"/>
@@ -3372,7 +3380,7 @@
       <c r="C88" s="8"/>
       <c r="D88" s="7"/>
       <c r="E88" s="7" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F88" s="7"/>
       <c r="G88" s="7"/>
@@ -3381,13 +3389,13 @@
       <c r="A89" s="7"/>
       <c r="B89" s="7"/>
       <c r="C89" s="8" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D89" s="7" t="s">
         <v>23</v>
       </c>
       <c r="E89" s="7" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F89" s="7"/>
       <c r="G89" s="7"/>
@@ -3405,17 +3413,17 @@
     </row>
     <row r="91" spans="1:7" ht="40.5">
       <c r="A91" s="4" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B91" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="C91" s="5" t="s">
         <v>54</v>
-      </c>
-      <c r="C91" s="5" t="s">
-        <v>55</v>
       </c>
       <c r="D91" s="4"/>
       <c r="E91" s="4" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F91" s="4" t="s">
         <v>13</v>
@@ -3428,10 +3436,10 @@
       <c r="C92" s="8"/>
       <c r="D92" s="7"/>
       <c r="E92" s="7" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F92" s="7" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G92" s="7"/>
     </row>
@@ -3452,7 +3460,7 @@
       <c r="C94" s="8"/>
       <c r="D94" s="7"/>
       <c r="E94" s="7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F94" s="7"/>
       <c r="G94" s="7"/>
@@ -3472,7 +3480,7 @@
       <c r="A96" s="7"/>
       <c r="B96" s="7"/>
       <c r="C96" s="8" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D96" s="7"/>
       <c r="E96" s="7" t="s">
@@ -3509,7 +3517,7 @@
       <c r="C99" s="8"/>
       <c r="D99" s="7"/>
       <c r="E99" s="7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F99" s="7"/>
       <c r="G99" s="7"/>
@@ -3518,10 +3526,10 @@
       <c r="A100" s="7"/>
       <c r="B100" s="7"/>
       <c r="C100" s="8" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D100" s="7" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E100" s="7" t="s">
         <v>4</v>
@@ -3535,7 +3543,7 @@
       <c r="C101" s="8"/>
       <c r="D101" s="7"/>
       <c r="E101" s="12" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F101" s="7"/>
       <c r="G101" s="7"/>
@@ -3545,10 +3553,10 @@
       <c r="B102" s="7"/>
       <c r="C102" s="8"/>
       <c r="D102" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="E102" s="7" t="s">
         <v>118</v>
-      </c>
-      <c r="E102" s="7" t="s">
-        <v>119</v>
       </c>
       <c r="F102" s="7"/>
       <c r="G102" s="7"/>
@@ -3558,10 +3566,10 @@
       <c r="B103" s="7"/>
       <c r="C103" s="8"/>
       <c r="D103" s="7" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E103" s="7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F103" s="7"/>
       <c r="G103" s="7"/>
@@ -3581,10 +3589,10 @@
       <c r="A105" s="7"/>
       <c r="B105" s="7"/>
       <c r="C105" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="D105" s="7" t="s">
         <v>78</v>
-      </c>
-      <c r="D105" s="7" t="s">
-        <v>79</v>
       </c>
       <c r="E105" s="7" t="s">
         <v>6</v>
@@ -3600,24 +3608,24 @@
       </c>
       <c r="D106" s="7"/>
       <c r="E106" s="10" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="F106" s="7"/>
       <c r="G106" s="10"/>
     </row>
     <row r="107" spans="1:7" ht="40.5">
       <c r="A107" s="4" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B107" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="C107" s="5" t="s">
         <v>54</v>
-      </c>
-      <c r="C107" s="5" t="s">
-        <v>55</v>
       </c>
       <c r="D107" s="4"/>
       <c r="E107" s="4" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="F107" s="4" t="s">
         <v>13</v>
@@ -3630,10 +3638,10 @@
       <c r="C108" s="8"/>
       <c r="D108" s="7"/>
       <c r="E108" s="7" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F108" s="7" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G108" s="7"/>
     </row>
@@ -3643,7 +3651,7 @@
       <c r="C109" s="8"/>
       <c r="D109" s="7"/>
       <c r="E109" s="7" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F109" s="7"/>
       <c r="G109" s="7"/>
@@ -3654,7 +3662,7 @@
       <c r="C110" s="8"/>
       <c r="D110" s="7"/>
       <c r="E110" s="7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F110" s="7"/>
       <c r="G110" s="7"/>
@@ -3665,7 +3673,7 @@
       <c r="C111" s="8"/>
       <c r="D111" s="7"/>
       <c r="E111" s="12" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F111" s="7"/>
       <c r="G111" s="7"/>
@@ -3674,7 +3682,7 @@
       <c r="A112" s="7"/>
       <c r="B112" s="7"/>
       <c r="C112" s="8" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D112" s="7"/>
       <c r="E112" s="7" t="s">
@@ -3700,7 +3708,7 @@
       <c r="C114" s="8"/>
       <c r="D114" s="7"/>
       <c r="E114" s="7" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F114" s="7"/>
       <c r="G114" s="7"/>
@@ -3711,7 +3719,7 @@
       <c r="C115" s="8"/>
       <c r="D115" s="7"/>
       <c r="E115" s="7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F115" s="7"/>
       <c r="G115" s="7"/>
@@ -3720,10 +3728,10 @@
       <c r="A116" s="7"/>
       <c r="B116" s="7"/>
       <c r="C116" s="8" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D116" s="7" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E116" s="7" t="s">
         <v>4</v>
@@ -3737,7 +3745,7 @@
       <c r="C117" s="8"/>
       <c r="D117" s="7"/>
       <c r="E117" s="12" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F117" s="7"/>
       <c r="G117" s="7"/>
@@ -3747,10 +3755,10 @@
       <c r="B118" s="7"/>
       <c r="C118" s="8"/>
       <c r="D118" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="E118" s="7" t="s">
         <v>118</v>
-      </c>
-      <c r="E118" s="7" t="s">
-        <v>119</v>
       </c>
       <c r="F118" s="7"/>
       <c r="G118" s="7"/>
@@ -3760,10 +3768,10 @@
       <c r="B119" s="7"/>
       <c r="C119" s="8"/>
       <c r="D119" s="7" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E119" s="7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F119" s="7"/>
       <c r="G119" s="7"/>
@@ -3783,10 +3791,10 @@
       <c r="A121" s="7"/>
       <c r="B121" s="7"/>
       <c r="C121" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="D121" s="7" t="s">
         <v>78</v>
-      </c>
-      <c r="D121" s="7" t="s">
-        <v>79</v>
       </c>
       <c r="E121" s="7" t="s">
         <v>6</v>
@@ -3802,17 +3810,17 @@
       </c>
       <c r="D122" s="7"/>
       <c r="E122" s="10" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="F122" s="7"/>
       <c r="G122" s="10"/>
     </row>
     <row r="123" spans="1:7" ht="40.5">
       <c r="A123" s="4" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B123" s="4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C123" s="5"/>
       <c r="D123" s="4"/>
@@ -3831,7 +3839,7 @@
       <c r="D124" s="7"/>
       <c r="E124" s="7"/>
       <c r="F124" s="7" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G124" s="7"/>
     </row>
@@ -3846,10 +3854,10 @@
     </row>
     <row r="126" spans="1:7" ht="40.5">
       <c r="A126" s="4" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B126" s="4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C126" s="5"/>
       <c r="D126" s="4"/>
@@ -3865,14 +3873,14 @@
       <c r="A127" s="7"/>
       <c r="B127" s="7"/>
       <c r="C127" s="7" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D127" s="7"/>
       <c r="E127" s="7" t="s">
         <v>37</v>
       </c>
       <c r="F127" s="7" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G127" s="7"/>
     </row>
@@ -3887,10 +3895,10 @@
     </row>
     <row r="129" spans="1:7" ht="67.5">
       <c r="A129" s="4" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B129" s="4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C129" s="14" t="s">
         <v>39</v>
@@ -3923,22 +3931,22 @@
         <v>34</v>
       </c>
       <c r="B132" s="4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C132" s="5" t="s">
+        <v>130</v>
+      </c>
+      <c r="D132" s="4" t="s">
         <v>131</v>
       </c>
-      <c r="D132" s="4" t="s">
+      <c r="E132" s="4" t="s">
         <v>132</v>
       </c>
-      <c r="E132" s="4" t="s">
+      <c r="F132" s="4" t="s">
         <v>133</v>
       </c>
-      <c r="F132" s="4" t="s">
+      <c r="G132" s="4" t="s">
         <v>134</v>
-      </c>
-      <c r="G132" s="4" t="s">
-        <v>135</v>
       </c>
     </row>
     <row r="133" spans="1:7">
@@ -3947,7 +3955,7 @@
       <c r="C133" s="8"/>
       <c r="D133" s="7"/>
       <c r="E133" s="7" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F133" s="7"/>
       <c r="G133" s="7"/>
@@ -3978,16 +3986,16 @@
       <c r="A136" s="7"/>
       <c r="B136" s="7"/>
       <c r="C136" s="8" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D136" s="7" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E136" s="7" t="s">
         <v>35</v>
       </c>
       <c r="F136" s="7" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="G136" s="7"/>
     </row>
@@ -4007,7 +4015,7 @@
         <v>10</v>
       </c>
       <c r="B138" s="4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C138" s="5"/>
       <c r="D138" s="4"/>
@@ -4015,117 +4023,121 @@
       <c r="F138" s="4"/>
       <c r="G138" s="4"/>
     </row>
-    <row r="139" spans="1:7" ht="54">
+    <row r="139" spans="1:7" ht="40.5">
       <c r="A139" s="7"/>
       <c r="B139" s="7"/>
-      <c r="C139" s="7" t="s">
-        <v>139</v>
-      </c>
+      <c r="C139" s="7"/>
       <c r="D139" s="7"/>
-      <c r="E139" s="7"/>
+      <c r="E139" s="7" t="s">
+        <v>138</v>
+      </c>
       <c r="F139" s="7"/>
       <c r="G139" s="7"/>
     </row>
-    <row r="140" spans="1:7" ht="40.5">
+    <row r="140" spans="1:7" ht="27">
       <c r="A140" s="7"/>
       <c r="B140" s="7"/>
-      <c r="C140" s="7" t="s">
-        <v>140</v>
-      </c>
+      <c r="C140" s="7"/>
       <c r="D140" s="7"/>
-      <c r="E140" s="7"/>
-      <c r="F140" s="7"/>
+      <c r="E140" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="F140" s="7" t="s">
+        <v>142</v>
+      </c>
       <c r="G140" s="7"/>
     </row>
-    <row r="141" spans="1:7" ht="40.5">
+    <row r="141" spans="1:7" ht="27">
       <c r="A141" s="7"/>
       <c r="B141" s="7"/>
-      <c r="C141" s="7" t="s">
-        <v>42</v>
-      </c>
+      <c r="C141" s="7"/>
       <c r="D141" s="7"/>
-      <c r="E141" s="7"/>
-      <c r="F141" s="7"/>
+      <c r="E141" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="F141" s="7" t="s">
+        <v>57</v>
+      </c>
       <c r="G141" s="7"/>
     </row>
-    <row r="142" spans="1:7" ht="40.5">
+    <row r="142" spans="1:7" ht="27">
       <c r="A142" s="7"/>
       <c r="B142" s="7"/>
-      <c r="C142" s="7" t="s">
-        <v>43</v>
-      </c>
+      <c r="C142" s="7"/>
       <c r="D142" s="7"/>
-      <c r="E142" s="7"/>
-      <c r="F142" s="7"/>
+      <c r="E142" s="7" t="s">
+        <v>143</v>
+      </c>
+      <c r="F142" s="7" t="s">
+        <v>142</v>
+      </c>
       <c r="G142" s="7"/>
     </row>
-    <row r="143" spans="1:7" ht="40.5">
-      <c r="A143" s="4" t="s">
-        <v>141</v>
-      </c>
-      <c r="B143" s="4" t="s">
+    <row r="143" spans="1:7" ht="27">
+      <c r="A143" s="7"/>
+      <c r="B143" s="7"/>
+      <c r="C143" s="7"/>
+      <c r="D143" s="7"/>
+      <c r="E143" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="F143" s="7" t="s">
+        <v>142</v>
+      </c>
+      <c r="G143" s="7"/>
+    </row>
+    <row r="144" spans="1:7" ht="40.5">
+      <c r="A144" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="B144" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="C144" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="C143" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="D143" s="4"/>
-      <c r="E143" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="F143" s="4" t="s">
+      <c r="D144" s="4"/>
+      <c r="E144" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="F144" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G143" s="4"/>
-    </row>
-    <row r="144" spans="1:7">
-      <c r="A144" s="7"/>
-      <c r="B144" s="7"/>
-      <c r="C144" s="8"/>
-      <c r="D144" s="7"/>
-      <c r="E144" s="7" t="s">
-        <v>124</v>
-      </c>
-      <c r="F144" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="G144" s="7"/>
+      <c r="G144" s="4"/>
     </row>
     <row r="145" spans="1:7">
       <c r="A145" s="7"/>
       <c r="B145" s="7"/>
-      <c r="C145" s="8" t="s">
-        <v>63</v>
-      </c>
+      <c r="C145" s="8"/>
       <c r="D145" s="7"/>
       <c r="E145" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="F145" s="7"/>
+        <v>123</v>
+      </c>
+      <c r="F145" s="7" t="s">
+        <v>57</v>
+      </c>
       <c r="G145" s="7"/>
     </row>
     <row r="146" spans="1:7">
       <c r="A146" s="7"/>
       <c r="B146" s="7"/>
-      <c r="C146" s="8"/>
+      <c r="C146" s="8" t="s">
+        <v>62</v>
+      </c>
       <c r="D146" s="7"/>
       <c r="E146" s="7" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F146" s="7"/>
       <c r="G146" s="7"/>
     </row>
-    <row r="147" spans="1:7" ht="67.5">
+    <row r="147" spans="1:7">
       <c r="A147" s="7"/>
       <c r="B147" s="7"/>
-      <c r="C147" s="8" t="s">
-        <v>91</v>
-      </c>
-      <c r="D147" s="7" t="s">
-        <v>117</v>
-      </c>
+      <c r="C147" s="8"/>
+      <c r="D147" s="7"/>
       <c r="E147" s="7" t="s">
-        <v>119</v>
+        <v>7</v>
       </c>
       <c r="F147" s="7"/>
       <c r="G147" s="7"/>
@@ -4133,65 +4145,71 @@
     <row r="148" spans="1:7" ht="67.5">
       <c r="A148" s="7"/>
       <c r="B148" s="7"/>
-      <c r="C148" s="8"/>
+      <c r="C148" s="8" t="s">
+        <v>90</v>
+      </c>
       <c r="D148" s="7" t="s">
+        <v>116</v>
+      </c>
+      <c r="E148" s="7" t="s">
         <v>118</v>
-      </c>
-      <c r="E148" s="7" t="s">
-        <v>33</v>
       </c>
       <c r="F148" s="7"/>
       <c r="G148" s="7"/>
     </row>
-    <row r="149" spans="1:7" ht="27">
+    <row r="149" spans="1:7" ht="67.5">
       <c r="A149" s="7"/>
       <c r="B149" s="7"/>
-      <c r="C149" s="8" t="s">
-        <v>78</v>
-      </c>
+      <c r="C149" s="8"/>
       <c r="D149" s="7" t="s">
-        <v>79</v>
+        <v>117</v>
       </c>
       <c r="E149" s="7" t="s">
-        <v>6</v>
+        <v>33</v>
       </c>
       <c r="F149" s="7"/>
       <c r="G149" s="7"/>
     </row>
-    <row r="150" spans="1:7" ht="40.5">
+    <row r="150" spans="1:7" ht="27">
       <c r="A150" s="7"/>
       <c r="B150" s="7"/>
       <c r="C150" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="D150" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="E150" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="F150" s="7"/>
+      <c r="G150" s="7"/>
+    </row>
+    <row r="151" spans="1:7" ht="40.5">
+      <c r="A151" s="7"/>
+      <c r="B151" s="7"/>
+      <c r="C151" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="D150" s="7"/>
-      <c r="E150" s="10" t="s">
-        <v>121</v>
-      </c>
-      <c r="F150" s="7"/>
-      <c r="G150" s="10"/>
-    </row>
-    <row r="151" spans="1:7" ht="40.5">
-      <c r="A151" s="4" t="s">
-        <v>142</v>
-      </c>
-      <c r="B151" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="C151" s="5"/>
-      <c r="D151" s="4"/>
-      <c r="E151" s="4"/>
-      <c r="F151" s="4"/>
-      <c r="G151" s="4"/>
-    </row>
-    <row r="152" spans="1:7">
-      <c r="A152" s="7"/>
-      <c r="B152" s="7"/>
-      <c r="C152" s="8"/>
-      <c r="D152" s="7"/>
-      <c r="E152" s="7"/>
-      <c r="F152" s="7"/>
-      <c r="G152" s="7"/>
+      <c r="D151" s="7"/>
+      <c r="E151" s="10" t="s">
+        <v>120</v>
+      </c>
+      <c r="F151" s="7"/>
+      <c r="G151" s="10"/>
+    </row>
+    <row r="152" spans="1:7" ht="40.5">
+      <c r="A152" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="B152" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="C152" s="5"/>
+      <c r="D152" s="4"/>
+      <c r="E152" s="4"/>
+      <c r="F152" s="4"/>
+      <c r="G152" s="4"/>
     </row>
     <row r="153" spans="1:7">
       <c r="A153" s="7"/>
@@ -4203,13 +4221,22 @@
       <c r="G153" s="7"/>
     </row>
     <row r="154" spans="1:7">
-      <c r="D154" s="9"/>
-      <c r="E154" s="9"/>
-      <c r="F154" s="9"/>
-      <c r="G154" s="9"/>
+      <c r="A154" s="7"/>
+      <c r="B154" s="7"/>
+      <c r="C154" s="8"/>
+      <c r="D154" s="7"/>
+      <c r="E154" s="7"/>
+      <c r="F154" s="7"/>
+      <c r="G154" s="7"/>
+    </row>
+    <row r="155" spans="1:7">
+      <c r="D155" s="9"/>
+      <c r="E155" s="9"/>
+      <c r="F155" s="9"/>
+      <c r="G155" s="9"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G142"/>
+  <autoFilter ref="A1:G143"/>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/internal_doc/05.测试设计/可靠性测试/主子表故障测试_review.xlsx
+++ b/internal_doc/05.测试设计/可靠性测试/主子表故障测试_review.xlsx
@@ -4,12 +4,11 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="6090" yWindow="120" windowWidth="18120" windowHeight="7890"/>
+    <workbookView xWindow="6090" yWindow="120" windowWidth="17940" windowHeight="7890"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
-    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
+    <sheet name="Sheet3" sheetId="3" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$G$143</definedName>
@@ -76,6 +75,32 @@
         </r>
       </text>
     </comment>
+    <comment ref="E6" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Author:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+不用测试</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="F6" authorId="0">
       <text>
         <r>
@@ -147,6 +172,32 @@
         </r>
       </text>
     </comment>
+    <comment ref="E11" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Author:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+不用测试</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="F12" authorId="0">
       <text>
         <r>
@@ -199,6 +250,32 @@
         </r>
       </text>
     </comment>
+    <comment ref="D14" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Author:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+高优先级</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="F15" authorId="0">
       <text>
         <r>
@@ -260,6 +337,32 @@
         </r>
       </text>
     </comment>
+    <comment ref="D17" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Author:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+主子表其他基本操作需要补充测试点</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="C20" authorId="0">
       <text>
         <r>
@@ -329,6 +432,32 @@
         </r>
       </text>
     </comment>
+    <comment ref="C23" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Author:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+优先级放低</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="E36" authorId="0">
       <text>
         <r>
@@ -351,6 +480,32 @@
             <charset val="134"/>
           </rPr>
           <t>不需要考虑</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F44" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Author:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+在结果中关注，不单独测试网络拥塞选主</t>
         </r>
       </text>
     </comment>
@@ -580,6 +735,40 @@
         </r>
       </text>
     </comment>
+    <comment ref="A85" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Author:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+systemspace</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t>撑满</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="E85" authorId="0">
       <text>
         <r>
@@ -970,6 +1159,32 @@
           <t xml:space="preserve">
 跟断网一样
 需要考虑几个节点组合的场景</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E141" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Author:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+数据节点网络单通情况放在基本操作里面测试（余婷）</t>
         </r>
       </text>
     </comment>
@@ -1069,15 +1284,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="352" uniqueCount="145">
-  <si>
-    <t>dataRG连续降备</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>dataRG备节点故障</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="331" uniqueCount="148">
   <si>
     <t>dataRG主节点所在服务器CPU耗尽</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1099,9 +1306,6 @@
     <t>catalog备节点异常重启</t>
   </si>
   <si>
-    <t>dataRG主节点异常重启</t>
-  </si>
-  <si>
     <t>catalog主节点异常重启</t>
   </si>
   <si>
@@ -1214,10 +1418,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>等友滨确认后再考虑具体测试点</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>dataRG备节点XX异常</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1231,10 +1431,6 @@
   </si>
   <si>
     <t>闪断不超过选主的最小时间7s则不触发选主，attachCL成功，在主表做基本操作成功；闪断超过7s后组内重新选主，恢复网络后查看是否从新的主节点同步数据，数据完整且跟新主数据一致；挂载成功在对应主表做基本操作成功(如insert数据)；</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>网络拥塞达到选主条件时重新选主；恢复网络后查看是否从新的主节点同步数据，数据完整且跟新主数据一致；挂载成功在对应主表做基本操作成功(如insert数据)；</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -1685,6 +1881,39 @@
   </si>
   <si>
     <t>dataRG备节点与其他备节点网络单通</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>在主表insert大量数据</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>在主表upsert大量数据</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>在主表remove大量数据</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>在主表做aggregate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>网络拥塞达到选主条件时重新选主；恢复网络后查看是否从新的主节点同步数据，数据完整且跟新主数据一致；挂载成功在对应主表做基本操作成功(如insert数据)；</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>insert/upsert/remove
+两个分区组各挂载一个子表，在同一个coord操作，其中一个分区组不停挂载和分离子表，另外一个做基本操作，测试编目信息旧的情况</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>不考虑</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>编目节点异常kill-9、kill -15(并发)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2185,43 +2414,43 @@
   <sheetData>
     <row r="1" spans="1:7" s="3" customFormat="1" ht="27">
       <c r="A1" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="F1" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="G1" s="2" t="s">
         <v>46</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>51</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="40.5">
       <c r="A2" s="4" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="D2" s="4"/>
       <c r="E2" s="4" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G2" s="4"/>
     </row>
@@ -2231,10 +2460,10 @@
       <c r="C3" s="8"/>
       <c r="D3" s="7"/>
       <c r="E3" s="7" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="F3" s="7" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="G3" s="7"/>
     </row>
@@ -2244,10 +2473,10 @@
       <c r="C4" s="8"/>
       <c r="D4" s="7"/>
       <c r="E4" s="7" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="G4" s="7"/>
     </row>
@@ -2257,10 +2486,10 @@
       <c r="C5" s="8"/>
       <c r="D5" s="7"/>
       <c r="E5" s="7" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="G5" s="7"/>
     </row>
@@ -2270,10 +2499,10 @@
       <c r="C6" s="8"/>
       <c r="D6" s="7"/>
       <c r="E6" s="7" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="G6" s="7"/>
     </row>
@@ -2281,14 +2510,14 @@
       <c r="A7" s="7"/>
       <c r="B7" s="7"/>
       <c r="C7" s="8" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="D7" s="7"/>
       <c r="E7" s="7" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="F7" s="7" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G7" s="7"/>
     </row>
@@ -2298,10 +2527,10 @@
       <c r="C8" s="8"/>
       <c r="D8" s="7"/>
       <c r="E8" s="7" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="G8" s="7"/>
     </row>
@@ -2311,10 +2540,10 @@
       <c r="C9" s="8"/>
       <c r="D9" s="7"/>
       <c r="E9" s="7" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G9" s="7"/>
     </row>
@@ -2324,10 +2553,10 @@
       <c r="C10" s="8"/>
       <c r="D10" s="7"/>
       <c r="E10" s="7" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="F10" s="7" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="G10" s="7"/>
     </row>
@@ -2337,10 +2566,10 @@
       <c r="C11" s="8"/>
       <c r="D11" s="7"/>
       <c r="E11" s="7" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="F11" s="7" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="G11" s="7"/>
     </row>
@@ -2348,16 +2577,16 @@
       <c r="A12" s="7"/>
       <c r="B12" s="7"/>
       <c r="C12" s="8" t="s">
-        <v>63</v>
+        <v>140</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="F12" s="7" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="G12" s="7"/>
     </row>
@@ -2367,7 +2596,7 @@
       <c r="C13" s="8"/>
       <c r="D13" s="7"/>
       <c r="E13" s="11" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="F13" s="7"/>
       <c r="G13" s="7"/>
@@ -2377,13 +2606,13 @@
       <c r="B14" s="7"/>
       <c r="C14" s="8"/>
       <c r="D14" s="7" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="F14" s="7" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="G14" s="7"/>
     </row>
@@ -2392,13 +2621,13 @@
       <c r="B15" s="7"/>
       <c r="C15" s="8"/>
       <c r="D15" s="7" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="E15" s="7" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="F15" s="7" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="G15" s="7"/>
     </row>
@@ -2408,10 +2637,10 @@
       <c r="C16" s="8"/>
       <c r="D16" s="7"/>
       <c r="E16" s="7" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="F16" s="7" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="G16" s="7"/>
     </row>
@@ -2419,16 +2648,16 @@
       <c r="A17" s="7"/>
       <c r="B17" s="7"/>
       <c r="C17" s="8" t="s">
-        <v>70</v>
+        <v>141</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="E17" s="7" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="F17" s="7" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="G17" s="7"/>
     </row>
@@ -2438,10 +2667,10 @@
       <c r="C18" s="8"/>
       <c r="D18" s="7"/>
       <c r="E18" s="7" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="F18" s="7" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="G18" s="7"/>
     </row>
@@ -2451,10 +2680,10 @@
       <c r="C19" s="8"/>
       <c r="D19" s="7"/>
       <c r="E19" s="7" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="F19" s="7" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="G19" s="7"/>
     </row>
@@ -2462,16 +2691,16 @@
       <c r="A20" s="7"/>
       <c r="B20" s="7"/>
       <c r="C20" s="8" t="s">
-        <v>74</v>
+        <v>142</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="E20" s="7" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="F20" s="7" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="G20" s="7"/>
     </row>
@@ -2481,10 +2710,10 @@
       <c r="C21" s="8"/>
       <c r="D21" s="7"/>
       <c r="E21" s="7" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="F21" s="7" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="G21" s="7"/>
     </row>
@@ -2492,16 +2721,16 @@
       <c r="A22" s="7"/>
       <c r="B22" s="7"/>
       <c r="C22" s="8" t="s">
-        <v>77</v>
+        <v>143</v>
       </c>
       <c r="D22" s="7" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="E22" s="7" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="F22" s="7" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="G22" s="7"/>
     </row>
@@ -2509,36 +2738,36 @@
       <c r="A23" s="7"/>
       <c r="B23" s="7"/>
       <c r="C23" s="8" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="D23" s="7"/>
       <c r="E23" s="7" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="F23" s="7" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="G23" s="7"/>
     </row>
     <row r="24" spans="1:7" ht="54">
       <c r="A24" s="4" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="D24" s="4"/>
       <c r="E24" s="4" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="F24" s="4" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="G24" s="4" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -2547,10 +2776,10 @@
       <c r="C25" s="8"/>
       <c r="D25" s="7"/>
       <c r="E25" s="7" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F25" s="7" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="G25" s="7"/>
     </row>
@@ -2560,7 +2789,7 @@
       <c r="C26" s="8"/>
       <c r="D26" s="7"/>
       <c r="E26" s="7" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="F26" s="7"/>
       <c r="G26" s="7"/>
@@ -2571,7 +2800,7 @@
       <c r="C27" s="8"/>
       <c r="D27" s="7"/>
       <c r="E27" s="7" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="F27" s="7"/>
       <c r="G27" s="7"/>
@@ -2582,7 +2811,7 @@
       <c r="C28" s="8"/>
       <c r="D28" s="7"/>
       <c r="E28" s="7" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="F28" s="7"/>
       <c r="G28" s="7"/>
@@ -2591,11 +2820,11 @@
       <c r="A29" s="7"/>
       <c r="B29" s="7"/>
       <c r="C29" s="8" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="D29" s="7"/>
       <c r="E29" s="7" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F29" s="7"/>
       <c r="G29" s="7"/>
@@ -2606,7 +2835,7 @@
       <c r="C30" s="8"/>
       <c r="D30" s="7"/>
       <c r="E30" s="7" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F30" s="7"/>
       <c r="G30" s="7"/>
@@ -2617,7 +2846,7 @@
       <c r="C31" s="8"/>
       <c r="D31" s="7"/>
       <c r="E31" s="7" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="F31" s="7"/>
       <c r="G31" s="7"/>
@@ -2628,7 +2857,7 @@
       <c r="C32" s="8"/>
       <c r="D32" s="7"/>
       <c r="E32" s="7" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="F32" s="7"/>
       <c r="G32" s="7"/>
@@ -2639,7 +2868,7 @@
       <c r="C33" s="8"/>
       <c r="D33" s="7"/>
       <c r="E33" s="7" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="F33" s="7"/>
       <c r="G33" s="7"/>
@@ -2648,13 +2877,13 @@
       <c r="A34" s="7"/>
       <c r="B34" s="7"/>
       <c r="C34" s="8" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="D34" s="7" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="E34" s="7" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F34" s="7"/>
       <c r="G34" s="7"/>
@@ -2665,7 +2894,7 @@
       <c r="C35" s="8"/>
       <c r="D35" s="7"/>
       <c r="E35" s="7" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F35" s="7"/>
       <c r="G35" s="7"/>
@@ -2675,10 +2904,10 @@
       <c r="B36" s="7"/>
       <c r="C36" s="8"/>
       <c r="D36" s="7" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="E36" s="12" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="F36" s="7"/>
       <c r="G36" s="7"/>
@@ -2688,10 +2917,10 @@
       <c r="B37" s="7"/>
       <c r="C37" s="8"/>
       <c r="D37" s="7" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="E37" s="7" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="F37" s="7"/>
       <c r="G37" s="7"/>
@@ -2700,13 +2929,13 @@
       <c r="A38" s="7"/>
       <c r="B38" s="7"/>
       <c r="C38" s="8" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="D38" s="7" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="E38" s="7" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F38" s="7"/>
       <c r="G38" s="7"/>
@@ -2717,7 +2946,7 @@
       <c r="C39" s="8"/>
       <c r="D39" s="7"/>
       <c r="E39" s="7" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="F39" s="7"/>
       <c r="G39" s="7"/>
@@ -2726,13 +2955,13 @@
       <c r="A40" s="7"/>
       <c r="B40" s="7"/>
       <c r="C40" s="8" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="D40" s="7" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="E40" s="7" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F40" s="7"/>
       <c r="G40" s="7"/>
@@ -2743,7 +2972,7 @@
       <c r="C41" s="8"/>
       <c r="D41" s="7"/>
       <c r="E41" s="7" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="F41" s="7"/>
       <c r="G41" s="7"/>
@@ -2752,13 +2981,13 @@
       <c r="A42" s="7"/>
       <c r="B42" s="7"/>
       <c r="C42" s="8" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="D42" s="7" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="E42" s="7" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F42" s="7"/>
       <c r="G42" s="7"/>
@@ -2767,34 +2996,34 @@
       <c r="A43" s="7"/>
       <c r="B43" s="7"/>
       <c r="C43" s="8" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="D43" s="7"/>
       <c r="E43" s="7" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F43" s="7"/>
       <c r="G43" s="7"/>
     </row>
     <row r="44" spans="1:7" ht="40.5">
       <c r="A44" s="4" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="D44" s="4"/>
       <c r="E44" s="4" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="F44" s="4" t="s">
-        <v>44</v>
+        <v>144</v>
       </c>
       <c r="G44" s="4" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -2803,10 +3032,10 @@
       <c r="C45" s="8"/>
       <c r="D45" s="7"/>
       <c r="E45" s="7" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F45" s="7" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="G45" s="7"/>
     </row>
@@ -2816,7 +3045,7 @@
       <c r="C46" s="8"/>
       <c r="D46" s="7"/>
       <c r="E46" s="7" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="F46" s="7"/>
       <c r="G46" s="7"/>
@@ -2827,7 +3056,7 @@
       <c r="C47" s="8"/>
       <c r="D47" s="7"/>
       <c r="E47" s="7" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="F47" s="7"/>
       <c r="G47" s="7"/>
@@ -2838,7 +3067,7 @@
       <c r="C48" s="8"/>
       <c r="D48" s="7"/>
       <c r="E48" s="12" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F48" s="7"/>
       <c r="G48" s="7"/>
@@ -2847,11 +3076,11 @@
       <c r="A49" s="7"/>
       <c r="B49" s="7"/>
       <c r="C49" s="8" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="D49" s="7"/>
       <c r="E49" s="7" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="F49" s="7"/>
       <c r="G49" s="7"/>
@@ -2862,7 +3091,7 @@
       <c r="C50" s="8"/>
       <c r="D50" s="7"/>
       <c r="E50" s="7" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F50" s="7"/>
       <c r="G50" s="7"/>
@@ -2873,7 +3102,7 @@
       <c r="C51" s="8"/>
       <c r="D51" s="7"/>
       <c r="E51" s="7" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="F51" s="7"/>
       <c r="G51" s="7"/>
@@ -2884,7 +3113,7 @@
       <c r="C52" s="8"/>
       <c r="D52" s="7"/>
       <c r="E52" s="7" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="F52" s="7"/>
       <c r="G52" s="7"/>
@@ -2893,13 +3122,13 @@
       <c r="A53" s="7"/>
       <c r="B53" s="7"/>
       <c r="C53" s="8" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="D53" s="7" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="E53" s="7" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="F53" s="7"/>
       <c r="G53" s="7"/>
@@ -2909,10 +3138,10 @@
       <c r="B54" s="7"/>
       <c r="C54" s="8"/>
       <c r="D54" s="7" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="E54" s="7" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="F54" s="7"/>
       <c r="G54" s="7"/>
@@ -2922,10 +3151,10 @@
       <c r="B55" s="7"/>
       <c r="C55" s="8"/>
       <c r="D55" s="7" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="E55" s="7" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="F55" s="7"/>
       <c r="G55" s="7"/>
@@ -2936,7 +3165,7 @@
       <c r="C56" s="8"/>
       <c r="D56" s="7"/>
       <c r="E56" s="7" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F56" s="7"/>
       <c r="G56" s="7"/>
@@ -2945,13 +3174,13 @@
       <c r="A57" s="7"/>
       <c r="B57" s="7"/>
       <c r="C57" s="8" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="D57" s="7" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="E57" s="7" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="F57" s="7"/>
       <c r="G57" s="7"/>
@@ -2962,7 +3191,7 @@
       <c r="C58" s="8"/>
       <c r="D58" s="7"/>
       <c r="E58" s="12" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="F58" s="7"/>
       <c r="G58" s="7"/>
@@ -2973,7 +3202,7 @@
       <c r="C59" s="8"/>
       <c r="D59" s="7"/>
       <c r="E59" s="7" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F59" s="7"/>
       <c r="G59" s="7"/>
@@ -2982,13 +3211,13 @@
       <c r="A60" s="7"/>
       <c r="B60" s="7"/>
       <c r="C60" s="8" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="D60" s="7" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="E60" s="7" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="F60" s="7"/>
       <c r="G60" s="7"/>
@@ -2999,7 +3228,7 @@
       <c r="C61" s="8"/>
       <c r="D61" s="7"/>
       <c r="E61" s="7" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F61" s="7"/>
       <c r="G61" s="7"/>
@@ -3008,13 +3237,13 @@
       <c r="A62" s="7"/>
       <c r="B62" s="7"/>
       <c r="C62" s="8" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="D62" s="7" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="E62" s="7" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="F62" s="7"/>
       <c r="G62" s="7"/>
@@ -3023,11 +3252,11 @@
       <c r="A63" s="7"/>
       <c r="B63" s="7"/>
       <c r="C63" s="8" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="D63" s="7"/>
       <c r="E63" s="7" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="F63" s="7"/>
       <c r="G63" s="7"/>
@@ -3043,20 +3272,20 @@
     </row>
     <row r="65" spans="1:7" ht="27">
       <c r="A65" s="4" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="B65" s="4" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="C65" s="5" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="D65" s="4"/>
       <c r="E65" s="4" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="F65" s="4" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="G65" s="4"/>
     </row>
@@ -3066,10 +3295,10 @@
       <c r="C66" s="8"/>
       <c r="D66" s="7"/>
       <c r="E66" s="7" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="F66" s="7" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="G66" s="7"/>
     </row>
@@ -3079,7 +3308,7 @@
       <c r="C67" s="8"/>
       <c r="D67" s="7"/>
       <c r="E67" s="7" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F67" s="7"/>
       <c r="G67" s="7"/>
@@ -3088,11 +3317,11 @@
       <c r="A68" s="7"/>
       <c r="B68" s="7"/>
       <c r="C68" s="8" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="D68" s="7"/>
       <c r="E68" s="7" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F68" s="7"/>
       <c r="G68" s="7"/>
@@ -3101,13 +3330,13 @@
       <c r="A69" s="7"/>
       <c r="B69" s="7"/>
       <c r="C69" s="8" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="D69" s="7" t="s">
-        <v>91</v>
+        <v>145</v>
       </c>
       <c r="E69" s="7" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F69" s="7"/>
       <c r="G69" s="7"/>
@@ -3118,27 +3347,27 @@
       <c r="C70" s="8"/>
       <c r="D70" s="7"/>
       <c r="E70" s="7" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F70" s="7"/>
       <c r="G70" s="7"/>
     </row>
     <row r="71" spans="1:7" ht="27">
       <c r="A71" s="4" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="B71" s="4" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="C71" s="5" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="D71" s="4"/>
       <c r="E71" s="4" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="F71" s="4" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="G71" s="4"/>
     </row>
@@ -3148,10 +3377,10 @@
       <c r="C72" s="8"/>
       <c r="D72" s="7"/>
       <c r="E72" s="7" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="F72" s="7" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="G72" s="7"/>
     </row>
@@ -3161,7 +3390,7 @@
       <c r="C73" s="8"/>
       <c r="D73" s="7"/>
       <c r="E73" s="7" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="F73" s="7"/>
       <c r="G73" s="7"/>
@@ -3170,11 +3399,11 @@
       <c r="A74" s="7"/>
       <c r="B74" s="7"/>
       <c r="C74" s="8" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="D74" s="7"/>
       <c r="E74" s="7" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="F74" s="7"/>
       <c r="G74" s="7"/>
@@ -3183,13 +3412,13 @@
       <c r="A75" s="7"/>
       <c r="B75" s="7"/>
       <c r="C75" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="D75" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="E75" s="7" t="s">
         <v>90</v>
-      </c>
-      <c r="D75" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="E75" s="7" t="s">
-        <v>95</v>
       </c>
       <c r="F75" s="7"/>
       <c r="G75" s="7"/>
@@ -3200,44 +3429,44 @@
       <c r="C76" s="8"/>
       <c r="D76" s="7"/>
       <c r="E76" s="7" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="F76" s="7"/>
       <c r="G76" s="7"/>
     </row>
     <row r="77" spans="1:7" ht="40.5">
       <c r="A77" s="4" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="B77" s="4" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="C77" s="5" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="D77" s="4"/>
       <c r="E77" s="4" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="F77" s="4" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="G77" s="4" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="78" spans="1:7" ht="40.5">
       <c r="A78" s="7"/>
       <c r="B78" s="7"/>
       <c r="C78" s="8" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="D78" s="7"/>
       <c r="E78" s="7" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F78" s="7" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="G78" s="7"/>
     </row>
@@ -3245,16 +3474,16 @@
       <c r="A79" s="7"/>
       <c r="B79" s="7"/>
       <c r="C79" s="8" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="D79" s="7" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="E79" s="7" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="F79" s="7" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="G79" s="7"/>
     </row>
@@ -3264,42 +3493,42 @@
       <c r="C80" s="8"/>
       <c r="D80" s="7"/>
       <c r="E80" s="7" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F80" s="7" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="G80" s="7"/>
     </row>
     <row r="81" spans="1:7" ht="27">
       <c r="A81" s="4" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="B81" s="4" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="C81" s="4" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="D81" s="4"/>
       <c r="E81" s="4"/>
       <c r="F81" s="4" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="G81" s="4" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
     </row>
     <row r="82" spans="1:7" ht="27">
       <c r="A82" s="7"/>
       <c r="B82" s="7"/>
       <c r="C82" s="7" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="D82" s="7"/>
       <c r="E82" s="7"/>
       <c r="F82" s="7" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="G82" s="7"/>
     </row>
@@ -3307,12 +3536,12 @@
       <c r="A83" s="7"/>
       <c r="B83" s="7"/>
       <c r="C83" s="7" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="D83" s="7"/>
       <c r="E83" s="7"/>
       <c r="F83" s="7" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="G83" s="7"/>
     </row>
@@ -3320,31 +3549,31 @@
       <c r="A84" s="7"/>
       <c r="B84" s="7"/>
       <c r="C84" s="7" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="D84" s="7"/>
       <c r="E84" s="7"/>
       <c r="F84" s="7" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="G84" s="7"/>
     </row>
     <row r="85" spans="1:7" ht="27">
       <c r="A85" s="4" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="B85" s="4" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="C85" s="5" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="D85" s="4"/>
       <c r="E85" s="4" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="F85" s="4" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="G85" s="4"/>
     </row>
@@ -3354,10 +3583,10 @@
       <c r="C86" s="8"/>
       <c r="D86" s="7"/>
       <c r="E86" s="7" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="F86" s="7" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="G86" s="7"/>
     </row>
@@ -3365,11 +3594,11 @@
       <c r="A87" s="7"/>
       <c r="B87" s="7"/>
       <c r="C87" s="8" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="D87" s="7"/>
       <c r="E87" s="7" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="F87" s="7"/>
       <c r="G87" s="7"/>
@@ -3380,7 +3609,7 @@
       <c r="C88" s="8"/>
       <c r="D88" s="7"/>
       <c r="E88" s="7" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="F88" s="7"/>
       <c r="G88" s="7"/>
@@ -3389,13 +3618,13 @@
       <c r="A89" s="7"/>
       <c r="B89" s="7"/>
       <c r="C89" s="8" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="D89" s="7" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="E89" s="7" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="F89" s="7"/>
       <c r="G89" s="7"/>
@@ -3406,27 +3635,27 @@
       <c r="C90" s="8"/>
       <c r="D90" s="7"/>
       <c r="E90" s="7" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="F90" s="7"/>
       <c r="G90" s="7"/>
     </row>
     <row r="91" spans="1:7" ht="40.5">
       <c r="A91" s="4" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="B91" s="4" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="C91" s="5" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="D91" s="4"/>
       <c r="E91" s="4" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="F91" s="4" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="G91" s="4"/>
     </row>
@@ -3436,10 +3665,10 @@
       <c r="C92" s="8"/>
       <c r="D92" s="7"/>
       <c r="E92" s="7" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="F92" s="7" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="G92" s="7"/>
     </row>
@@ -3449,7 +3678,7 @@
       <c r="C93" s="8"/>
       <c r="D93" s="7"/>
       <c r="E93" s="7" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F93" s="7"/>
       <c r="G93" s="7"/>
@@ -3460,7 +3689,7 @@
       <c r="C94" s="8"/>
       <c r="D94" s="7"/>
       <c r="E94" s="7" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="F94" s="7"/>
       <c r="G94" s="7"/>
@@ -3471,7 +3700,7 @@
       <c r="C95" s="8"/>
       <c r="D95" s="7"/>
       <c r="E95" s="12" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="F95" s="7"/>
       <c r="G95" s="7"/>
@@ -3480,11 +3709,11 @@
       <c r="A96" s="7"/>
       <c r="B96" s="7"/>
       <c r="C96" s="8" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="D96" s="7"/>
       <c r="E96" s="7" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F96" s="7"/>
       <c r="G96" s="7"/>
@@ -3495,7 +3724,7 @@
       <c r="C97" s="8"/>
       <c r="D97" s="7"/>
       <c r="E97" s="7" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F97" s="7"/>
       <c r="G97" s="7"/>
@@ -3506,7 +3735,7 @@
       <c r="C98" s="8"/>
       <c r="D98" s="7"/>
       <c r="E98" s="7" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F98" s="7"/>
       <c r="G98" s="7"/>
@@ -3517,7 +3746,7 @@
       <c r="C99" s="8"/>
       <c r="D99" s="7"/>
       <c r="E99" s="7" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="F99" s="7"/>
       <c r="G99" s="7"/>
@@ -3526,13 +3755,13 @@
       <c r="A100" s="7"/>
       <c r="B100" s="7"/>
       <c r="C100" s="8" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="D100" s="7" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="E100" s="7" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F100" s="7"/>
       <c r="G100" s="7"/>
@@ -3543,7 +3772,7 @@
       <c r="C101" s="8"/>
       <c r="D101" s="7"/>
       <c r="E101" s="12" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="F101" s="7"/>
       <c r="G101" s="7"/>
@@ -3553,10 +3782,10 @@
       <c r="B102" s="7"/>
       <c r="C102" s="8"/>
       <c r="D102" s="7" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="E102" s="7" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="F102" s="7"/>
       <c r="G102" s="7"/>
@@ -3566,10 +3795,10 @@
       <c r="B103" s="7"/>
       <c r="C103" s="8"/>
       <c r="D103" s="7" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="E103" s="7" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="F103" s="7"/>
       <c r="G103" s="7"/>
@@ -3580,7 +3809,7 @@
       <c r="C104" s="8"/>
       <c r="D104" s="7"/>
       <c r="E104" s="7" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="F104" s="7"/>
       <c r="G104" s="7"/>
@@ -3589,13 +3818,13 @@
       <c r="A105" s="7"/>
       <c r="B105" s="7"/>
       <c r="C105" s="8" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="D105" s="7" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="E105" s="7" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F105" s="7"/>
       <c r="G105" s="7"/>
@@ -3604,31 +3833,31 @@
       <c r="A106" s="7"/>
       <c r="B106" s="7"/>
       <c r="C106" s="8" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="D106" s="7"/>
       <c r="E106" s="10" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="F106" s="7"/>
       <c r="G106" s="10"/>
     </row>
     <row r="107" spans="1:7" ht="40.5">
       <c r="A107" s="4" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="B107" s="4" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="C107" s="5" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="D107" s="4"/>
       <c r="E107" s="4" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="F107" s="4" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="G107" s="4"/>
     </row>
@@ -3638,10 +3867,10 @@
       <c r="C108" s="8"/>
       <c r="D108" s="7"/>
       <c r="E108" s="7" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="F108" s="7" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="G108" s="7"/>
     </row>
@@ -3651,7 +3880,7 @@
       <c r="C109" s="8"/>
       <c r="D109" s="7"/>
       <c r="E109" s="7" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="F109" s="7"/>
       <c r="G109" s="7"/>
@@ -3662,7 +3891,7 @@
       <c r="C110" s="8"/>
       <c r="D110" s="7"/>
       <c r="E110" s="7" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="F110" s="7"/>
       <c r="G110" s="7"/>
@@ -3673,7 +3902,7 @@
       <c r="C111" s="8"/>
       <c r="D111" s="7"/>
       <c r="E111" s="12" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="F111" s="7"/>
       <c r="G111" s="7"/>
@@ -3682,11 +3911,11 @@
       <c r="A112" s="7"/>
       <c r="B112" s="7"/>
       <c r="C112" s="8" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="D112" s="7"/>
       <c r="E112" s="7" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F112" s="7"/>
       <c r="G112" s="7"/>
@@ -3697,7 +3926,7 @@
       <c r="C113" s="8"/>
       <c r="D113" s="7"/>
       <c r="E113" s="7" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F113" s="7"/>
       <c r="G113" s="7"/>
@@ -3708,7 +3937,7 @@
       <c r="C114" s="8"/>
       <c r="D114" s="7"/>
       <c r="E114" s="7" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="F114" s="7"/>
       <c r="G114" s="7"/>
@@ -3719,7 +3948,7 @@
       <c r="C115" s="8"/>
       <c r="D115" s="7"/>
       <c r="E115" s="7" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="F115" s="7"/>
       <c r="G115" s="7"/>
@@ -3728,13 +3957,13 @@
       <c r="A116" s="7"/>
       <c r="B116" s="7"/>
       <c r="C116" s="8" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="D116" s="7" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="E116" s="7" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F116" s="7"/>
       <c r="G116" s="7"/>
@@ -3745,7 +3974,7 @@
       <c r="C117" s="8"/>
       <c r="D117" s="7"/>
       <c r="E117" s="12" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="F117" s="7"/>
       <c r="G117" s="7"/>
@@ -3755,10 +3984,10 @@
       <c r="B118" s="7"/>
       <c r="C118" s="8"/>
       <c r="D118" s="7" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="E118" s="7" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="F118" s="7"/>
       <c r="G118" s="7"/>
@@ -3768,10 +3997,10 @@
       <c r="B119" s="7"/>
       <c r="C119" s="8"/>
       <c r="D119" s="7" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="E119" s="7" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="F119" s="7"/>
       <c r="G119" s="7"/>
@@ -3782,7 +4011,7 @@
       <c r="C120" s="8"/>
       <c r="D120" s="7"/>
       <c r="E120" s="7" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="F120" s="7"/>
       <c r="G120" s="7"/>
@@ -3791,13 +4020,13 @@
       <c r="A121" s="7"/>
       <c r="B121" s="7"/>
       <c r="C121" s="8" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="D121" s="7" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="E121" s="7" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F121" s="7"/>
       <c r="G121" s="7"/>
@@ -3806,27 +4035,27 @@
       <c r="A122" s="7"/>
       <c r="B122" s="7"/>
       <c r="C122" s="8" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="D122" s="7"/>
       <c r="E122" s="10" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="F122" s="7"/>
       <c r="G122" s="10"/>
     </row>
     <row r="123" spans="1:7" ht="40.5">
       <c r="A123" s="4" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="B123" s="4" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="C123" s="5"/>
       <c r="D123" s="4"/>
       <c r="E123" s="4"/>
       <c r="F123" s="4" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="G123" s="4"/>
     </row>
@@ -3834,12 +4063,12 @@
       <c r="A124" s="7"/>
       <c r="B124" s="7"/>
       <c r="C124" s="7" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="D124" s="7"/>
       <c r="E124" s="7"/>
       <c r="F124" s="7" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="G124" s="7"/>
     </row>
@@ -3854,18 +4083,18 @@
     </row>
     <row r="126" spans="1:7" ht="40.5">
       <c r="A126" s="4" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="B126" s="4" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="C126" s="5"/>
       <c r="D126" s="4"/>
       <c r="E126" s="4" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="F126" s="4" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="G126" s="4"/>
     </row>
@@ -3873,14 +4102,14 @@
       <c r="A127" s="7"/>
       <c r="B127" s="7"/>
       <c r="C127" s="7" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="D127" s="7"/>
       <c r="E127" s="7" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="F127" s="7" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="G127" s="7"/>
     </row>
@@ -3895,13 +4124,13 @@
     </row>
     <row r="129" spans="1:7" ht="67.5">
       <c r="A129" s="4" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="B129" s="4" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="C129" s="14" t="s">
-        <v>39</v>
+        <v>146</v>
       </c>
       <c r="D129" s="4"/>
       <c r="E129" s="4"/>
@@ -3928,34 +4157,36 @@
     </row>
     <row r="132" spans="1:7" ht="54">
       <c r="A132" s="4" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="B132" s="4" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="C132" s="5" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="D132" s="4" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="E132" s="4" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="F132" s="4" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="G132" s="4" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="133" spans="1:7">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="133" spans="1:7" ht="27">
       <c r="A133" s="7"/>
       <c r="B133" s="7"/>
       <c r="C133" s="8"/>
-      <c r="D133" s="7"/>
+      <c r="D133" s="7" t="s">
+        <v>147</v>
+      </c>
       <c r="E133" s="7" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="F133" s="7"/>
       <c r="G133" s="7"/>
@@ -3966,7 +4197,7 @@
       <c r="C134" s="8"/>
       <c r="D134" s="7"/>
       <c r="E134" s="7" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="F134" s="7"/>
       <c r="G134" s="7"/>
@@ -3977,7 +4208,7 @@
       <c r="C135" s="8"/>
       <c r="D135" s="7"/>
       <c r="E135" s="7" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="F135" s="7"/>
       <c r="G135" s="7"/>
@@ -3986,16 +4217,16 @@
       <c r="A136" s="7"/>
       <c r="B136" s="7"/>
       <c r="C136" s="8" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="D136" s="7" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="E136" s="7" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="F136" s="7" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="G136" s="7"/>
     </row>
@@ -4005,17 +4236,17 @@
       <c r="C137" s="8"/>
       <c r="D137" s="7"/>
       <c r="E137" s="7" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="F137" s="7"/>
       <c r="G137" s="7"/>
     </row>
     <row r="138" spans="1:7" ht="40.5">
       <c r="A138" s="4" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B138" s="4" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="C138" s="5"/>
       <c r="D138" s="4"/>
@@ -4029,7 +4260,7 @@
       <c r="C139" s="7"/>
       <c r="D139" s="7"/>
       <c r="E139" s="7" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="F139" s="7"/>
       <c r="G139" s="7"/>
@@ -4040,10 +4271,10 @@
       <c r="C140" s="7"/>
       <c r="D140" s="7"/>
       <c r="E140" s="7" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="F140" s="7" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="G140" s="7"/>
     </row>
@@ -4053,10 +4284,10 @@
       <c r="C141" s="7"/>
       <c r="D141" s="7"/>
       <c r="E141" s="7" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="F141" s="7" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="G141" s="7"/>
     </row>
@@ -4066,10 +4297,10 @@
       <c r="C142" s="7"/>
       <c r="D142" s="7"/>
       <c r="E142" s="7" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="F142" s="7" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="G142" s="7"/>
     </row>
@@ -4079,29 +4310,29 @@
       <c r="C143" s="7"/>
       <c r="D143" s="7"/>
       <c r="E143" s="7" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="F143" s="7" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="G143" s="7"/>
     </row>
     <row r="144" spans="1:7" ht="40.5">
       <c r="A144" s="4" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="B144" s="4" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="C144" s="5" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="D144" s="4"/>
       <c r="E144" s="4" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="F144" s="4" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="G144" s="4"/>
     </row>
@@ -4111,10 +4342,10 @@
       <c r="C145" s="8"/>
       <c r="D145" s="7"/>
       <c r="E145" s="7" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="F145" s="7" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="G145" s="7"/>
     </row>
@@ -4122,11 +4353,11 @@
       <c r="A146" s="7"/>
       <c r="B146" s="7"/>
       <c r="C146" s="8" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="D146" s="7"/>
       <c r="E146" s="7" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F146" s="7"/>
       <c r="G146" s="7"/>
@@ -4137,7 +4368,7 @@
       <c r="C147" s="8"/>
       <c r="D147" s="7"/>
       <c r="E147" s="7" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F147" s="7"/>
       <c r="G147" s="7"/>
@@ -4146,13 +4377,13 @@
       <c r="A148" s="7"/>
       <c r="B148" s="7"/>
       <c r="C148" s="8" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="D148" s="7" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="E148" s="7" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="F148" s="7"/>
       <c r="G148" s="7"/>
@@ -4162,10 +4393,10 @@
       <c r="B149" s="7"/>
       <c r="C149" s="8"/>
       <c r="D149" s="7" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="E149" s="7" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="F149" s="7"/>
       <c r="G149" s="7"/>
@@ -4174,13 +4405,13 @@
       <c r="A150" s="7"/>
       <c r="B150" s="7"/>
       <c r="C150" s="8" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="D150" s="7" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="E150" s="7" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F150" s="7"/>
       <c r="G150" s="7"/>
@@ -4189,21 +4420,21 @@
       <c r="A151" s="7"/>
       <c r="B151" s="7"/>
       <c r="C151" s="8" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="D151" s="7"/>
       <c r="E151" s="10" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="F151" s="7"/>
       <c r="G151" s="10"/>
     </row>
     <row r="152" spans="1:7" ht="40.5">
       <c r="A152" s="4" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="B152" s="4" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="C152" s="5"/>
       <c r="D152" s="4"/>
@@ -4246,130 +4477,6 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A22"/>
-  <sheetFormatPr defaultRowHeight="13.5"/>
-  <cols>
-    <col min="1" max="1" width="22" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" s="7" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1">
-      <c r="A2" s="7" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="7" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1">
-      <c r="A4" s="7" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1">
-      <c r="A5" s="7" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1">
-      <c r="A6" s="7" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1">
-      <c r="A7" s="7" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1">
-      <c r="A8" s="7" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1">
-      <c r="A9" s="7" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:1">
-      <c r="A10" s="7" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1">
-      <c r="A11" s="7" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1">
-      <c r="A12" s="7" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="13" spans="1:1">
-      <c r="A13" s="7" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:1">
-      <c r="A14" s="7" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:1">
-      <c r="A15" s="7" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="16" spans="1:1">
-      <c r="A16" s="7" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1">
-      <c r="A17" s="7" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1">
-      <c r="A18" s="7" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1">
-      <c r="A19" s="7" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:1">
-      <c r="A20" s="7" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1">
-      <c r="A21" s="7" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="22" spans="1:1">
-      <c r="A22" s="7" t="s">
-        <v>9</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <sheetData/>
